--- a/docs/xlsx/jobs-2026-10-14.xlsx
+++ b/docs/xlsx/jobs-2026-10-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="680">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,1572 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Alaska Maritime NWR - Biological Science Technician (Avian)</t>
+  </si>
+  <si>
+    <t>USFWS - Alaska Maritime National Wildlife Refuge</t>
+  </si>
+  <si>
+    <t>Homer, AK</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19.52 - $31.43 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-alaska-maritime-nwr---biological-science-technician-avian-homer-alaska/9841195859</t>
+  </si>
+  <si>
+    <t>Assistant Professor - Precision Ranching</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M AgriLife Research</t>
+  </si>
+  <si>
+    <t>Sonora and San Angelo, TX</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Compensation for this position is commensurate based on the selected candidate’s qualifications.</t>
+  </si>
+  <si>
+    <t>ecology-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor---precision-ranching-sonora-and-san-angelo-texas/3095351797</t>
+  </si>
+  <si>
+    <t>Avian Husbandry and Education Internship</t>
+  </si>
+  <si>
+    <t>Avian Conservation Center - Center for Birds of Prey</t>
+  </si>
+  <si>
+    <t>Awendaw, SC</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$200 - $400 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-avian-husbandry-and-education-internship-awendaw-south-carolina/4443359971</t>
+  </si>
+  <si>
+    <t>Community Assistance Fellow – AmeriCorps</t>
+  </si>
+  <si>
+    <t>Conservation Legacy Program: Stewards Individual Placements Program</t>
+  </si>
+  <si>
+    <t>Westlake Village, CA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-assistance-fellow--americorps-westlake-village-california/4884246627</t>
+  </si>
+  <si>
+    <t>Eagle Studies Field Technician</t>
+  </si>
+  <si>
+    <t>HawkWatch International</t>
+  </si>
+  <si>
+    <t>Salt Lake City, UT</t>
+  </si>
+  <si>
+    <t>$3,100 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eagle-studies-field-technician-salt-lake-city-utah/7390918559</t>
+  </si>
+  <si>
+    <t>Educational Farm Manager</t>
+  </si>
+  <si>
+    <t>Green River Preserve</t>
+  </si>
+  <si>
+    <t>Cedar Mountain, NC</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$40,000 - $45,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-educational-farm-manager-cedar-mountain-north-carolina/6470617774</t>
+  </si>
+  <si>
+    <t>Environmental Science Educator</t>
+  </si>
+  <si>
+    <t>NatureBridge</t>
+  </si>
+  <si>
+    <t>Sausalito, CA</t>
+  </si>
+  <si>
+    <t>$17.14 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-science-educator-sausalito-california/1448174268</t>
+  </si>
+  <si>
+    <t>El Portal, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-science-educator-el-portal-california/4426815061</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Illinois Valley Watershed Council</t>
+  </si>
+  <si>
+    <t>Cave Junction, OR</t>
+  </si>
+  <si>
+    <t>$28.85 - $38.46 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-cave-junction-oregon/9096854027</t>
+  </si>
+  <si>
+    <t>Forester I</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Monticello, AR</t>
+  </si>
+  <si>
+    <t>Based on Experience</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forester-i-monticello-arkansas/1733786803</t>
+  </si>
+  <si>
+    <t>Grants &amp; Finance Specialist</t>
+  </si>
+  <si>
+    <t>Resource Conservation District of Santa Cruz County</t>
+  </si>
+  <si>
+    <t>Soquel, CA</t>
+  </si>
+  <si>
+    <t>$40.15 - $45.19 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grants--finance-specialist-soquel-california/3173852846</t>
+  </si>
+  <si>
+    <t>Heavy Equipment Operator (HEO)</t>
+  </si>
+  <si>
+    <t>CEMML</t>
+  </si>
+  <si>
+    <t>Flemington, GA</t>
+  </si>
+  <si>
+    <t>$20 - $30 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-heavy-equipment-operator-heo-flemington-georgia/3769773164</t>
+  </si>
+  <si>
+    <t>Otolith Laboratory Biologist - Fish &amp; Wildlife Biologist 3 - Permanent - 2026-08568</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$5,642 - $7,592 per month</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-otolith-laboratory-biologist---fish--wildlife-biologist-3---permanent---2026-08568-olympia-washington/5952151835</t>
+  </si>
+  <si>
+    <t>Part-time Avian Medical Internship</t>
+  </si>
+  <si>
+    <t>Avian Conservation Center</t>
+  </si>
+  <si>
+    <t>$200 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-part-time-avian-medical-internship-awendaw-south-carolina/5859784255</t>
+  </si>
+  <si>
+    <t>Primate Husbandry Internship Spring 2027</t>
+  </si>
+  <si>
+    <t>Lemur Conservation Foundation</t>
+  </si>
+  <si>
+    <t>Myakka City, FL</t>
+  </si>
+  <si>
+    <t>Unpaid, housing provided.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-primate-husbandry-internship-spring-2027-myakka-city-florida/2003226596</t>
+  </si>
+  <si>
+    <t>Program Associate</t>
+  </si>
+  <si>
+    <t>We Plant It Forward</t>
+  </si>
+  <si>
+    <t>Raleigh/Durham Area, NC</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-we-plant-it-forward-program-associate-raleighdurham-area-north-carolina/8352411068</t>
+  </si>
+  <si>
+    <t>Sea Turtle Lighting Biologist</t>
+  </si>
+  <si>
+    <t>Florida Fish &amp; Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>$21.63 per hour</t>
+  </si>
+  <si>
+    <t>marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sea-turtle-lighting-biologist-tallahassee-florida/9612224383</t>
+  </si>
+  <si>
+    <t>Senior Appraiser, Property and Acquisition Specialist</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>$6,542 - $8,801 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-appraiser-property-and-acquisition-specialist-olympia-washington/7397807574</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps- Crew Program Manager</t>
+  </si>
+  <si>
+    <t>Conservation Legacy</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>$58,800 - $60,564 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southeast-conservation-corps--crew-program-manager-chattanooga-tennessee/8373826136</t>
+  </si>
+  <si>
+    <t>State Heritage Botanist: Research Scientist 2</t>
+  </si>
+  <si>
+    <t>MN Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Sauk Rapids, MN</t>
+  </si>
+  <si>
+    <t>$68,841 - $101,476 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-heritage-botanist-research-scientist-2-sauk-rapids-minnesota/3534595062</t>
+  </si>
+  <si>
+    <t>Walking Mountains Graduate Fellowship 2027-2029</t>
+  </si>
+  <si>
+    <t>Walking Mountains</t>
+  </si>
+  <si>
+    <t>Avon, CO</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$17,500 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-walking-mountains-graduate-fellowship-2027-2029-avon-colorado/4193203099</t>
+  </si>
+  <si>
+    <t>Water Resources Director</t>
+  </si>
+  <si>
+    <t>Protect Our Water Jackson Hole</t>
+  </si>
+  <si>
+    <t>Jackson, WY</t>
+  </si>
+  <si>
+    <t>$90,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resources-director-jackson-wyoming/6042756887</t>
+  </si>
+  <si>
+    <t>Wildlife Technician (NPS, Mojave National Preserve)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Essex, CA</t>
+  </si>
+  <si>
+    <t>$22.50 per hour</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-technician-nps-mojave-national-preserve-essex-california/2229790015</t>
+  </si>
+  <si>
+    <t>Public Affairs Intern</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, California, United States</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/public-affairs-intern-8/</t>
+  </si>
+  <si>
+    <t>Administrative Assistant/Accounts Payable</t>
+  </si>
+  <si>
+    <t>New England Joint Board UNITE HERE</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f768fbdba9f490ba63b989dbb2bd08e-administrative-assistantaccounts-payable-new-england-joint-board-unite-here-boston</t>
+  </si>
+  <si>
+    <t>Administrative Specialist - Strategic Initiatives</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 30.93 - 40.17/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09eab3828a6342c98e9d59684e14625a-administrative-specialist-strategic-initiatives-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Administrator, High School Innovation</t>
+  </si>
+  <si>
+    <t>Michigan College Access Network</t>
+  </si>
+  <si>
+    <t>Lansing, Michigan</t>
+  </si>
+  <si>
+    <t>USD 54600.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c958fdf1d7694f65be02798ec23c231f-administrator-high-school-innovation-michigan-college-access-network-lansing</t>
+  </si>
+  <si>
+    <t>Adult Neuropsychologist — Coastal Wilmington, North Carolina</t>
+  </si>
+  <si>
+    <t>MARS Memory-Health Network</t>
+  </si>
+  <si>
+    <t>Wilmington, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5da3a07051764037a77a1b6ea25d4fa3-adult-neuropsychologist-coastal-wilmington-north-carolina-mars-memory-health-network-wilmington</t>
+  </si>
+  <si>
+    <t>Advancement Coordinator, Society of Fellows</t>
+  </si>
+  <si>
+    <t>The Huntington Library, Art Museum, and Botanical Gardens</t>
+  </si>
+  <si>
+    <t>San Marino, California</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 27.50/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ebf6662e7d940b6a5146c67c56a5c3c-advancement-coordinator-society-of-fellows-the-huntington-library-art-museum-and-botanical-gardens-san-marino</t>
+  </si>
+  <si>
+    <t>Assistant Director of Operations and Development</t>
+  </si>
+  <si>
+    <t>Phillips Brooks House Association</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Volunteering, Children Youth, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed833e77c6b14f66b34dbfb35e216c85-assistant-director-of-operations-and-development-phillips-brooks-house-association-cambridge</t>
+  </si>
+  <si>
+    <t>Assistant Director, CRM Special Projects</t>
+  </si>
+  <si>
+    <t>Hadassah, WZOA, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f7493d6cdff4e4fb9036a08306b6f00-assistant-director-crm-special-projects-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Division Director #463-26</t>
+  </si>
+  <si>
+    <t>New Jersey Department of Children and Families</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>Job Workplace, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3ee72e33c3e84a3b811115eadaad2d2d-assistant-division-director-463-26-new-jersey-department-of-children-and-families-trenton</t>
+  </si>
+  <si>
+    <t>Associate Director of Gift Planning Operations</t>
+  </si>
+  <si>
+    <t>Columbia University, Office of Alumni Relations and Development</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 83000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58b26b54beb24f19a31c48c8e8582755-associate-director-of-gift-planning-operations-columbia-university-office-of-alumni-relations-and-development-new-york</t>
+  </si>
+  <si>
+    <t>Associate General Counsel</t>
+  </si>
+  <si>
+    <t>International Association of Machinists &amp; Aerospace Workers</t>
+  </si>
+  <si>
+    <t>Upper Marlboro, Maryland</t>
+  </si>
+  <si>
+    <t>USD 130500.00 - 149600.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/457a99809336497da1eeb21de3c58086-associate-general-counsel-international-association-of-machinists-aerospace-workers-upper-marlboro</t>
+  </si>
+  <si>
+    <t>Associate Managing Director</t>
+  </si>
+  <si>
+    <t>Boynton Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba63129d31a14b60b49fe44b0e20dde3-associate-managing-director-hadassah-wzoa-inc-boynton-beach</t>
+  </si>
+  <si>
+    <t>Certified Middle School Math Teacher CT SY26-27</t>
+  </si>
+  <si>
+    <t>Excellence Community Schools</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 53235.00 - 118163.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/031c332c5dbc41b7b8e5c736ebd62557-certified-middle-school-math-teacher-ct-sy26-27-excellence-community-schools-stamford</t>
+  </si>
+  <si>
+    <t>Certified Middle School Science Teacher (CT) SY26-27</t>
+  </si>
+  <si>
+    <t>Stamford, CT</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c73712b97414b2786d55c1b881cb5ca-certified-middle-school-science-teacher-ct-sy26-27-excellence-community-schools-stamford</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Daughters of the American Revolution</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 270000.00 - 280000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f6956bc465654228aaebba7d95640558-chief-financial-officer-daughters-of-the-american-revolution-washington</t>
+  </si>
+  <si>
+    <t>Child Trauma Responder CTRT - HYBRID schedule</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>USD 29.70 - 30.80/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7371be190ea4b81807204b1ae9d8543-child-trauma-responder-ctrt-hybrid-schedule-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Communications Operations Manager</t>
+  </si>
+  <si>
+    <t>Friends Seminary</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04100178aadc413abd7e7e6c044d8a92-communications-operations-manager-friends-seminary-new-york</t>
+  </si>
+  <si>
+    <t>Community First! Senior Replication Manager</t>
+  </si>
+  <si>
+    <t>Mobile Loaves &amp; Fishes</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb175e2dc77e4e468c6f6810a4f5ee3a-community-first-senior-replication-manager-mobile-loaves-fishes-austin</t>
+  </si>
+  <si>
+    <t>Contract Lobbyist</t>
+  </si>
+  <si>
+    <t>Minnesota Center for Environmental Advocacy</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be21f1b310d5421fb5ff0193c94f59a3-contract-lobbyist-minnesota-center-for-environmental-advocacy-saint-paul</t>
+  </si>
+  <si>
+    <t>Data &amp; Customer Success, Senior Specialist</t>
+  </si>
+  <si>
+    <t>Grounded Solutions Network</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc64962e733d4b9e83f1a2c751d68a42-data-customer-success-senior-specialist-grounded-solutions-network-oakland</t>
+  </si>
+  <si>
+    <t>Database Manager</t>
+  </si>
+  <si>
+    <t>The Jewish Museum</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c45d8aeacc7d4e20bafd2cd8afff2615-database-manager-the-jewish-museum-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Chief, Development</t>
+  </si>
+  <si>
+    <t>Martha's Table</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c3b388fe3e64fe8bf9feabfbb906ec9-deputy-chief-development-marthas-table-washington</t>
+  </si>
+  <si>
+    <t>DEPUTY DIRECTOR OF ORGANIZING</t>
+  </si>
+  <si>
+    <t>Ohio Nurses Association</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/904d9162e05746c5877ad1b108d14047-deputy-director-of-organizing-ohio-nurses-association-columbus</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>SARASOTA HOUSING FUNDING CORP</t>
+  </si>
+  <si>
+    <t>Sarasota, Florida</t>
+  </si>
+  <si>
+    <t>USD 68700.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/876e24f27bb94689bf7d67d46bf7f54f-development-director-sarasota-housing-funding-corp-sarasota</t>
+  </si>
+  <si>
+    <t>Development Officer - Major Gifts</t>
+  </si>
+  <si>
+    <t>The Mountaineers</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8519507f03b4d30b1dd2199a1b2ec8b-development-officer-major-gifts-the-mountaineers-seattle</t>
+  </si>
+  <si>
+    <t>Digital Audience and News Producer</t>
+  </si>
+  <si>
+    <t>Maine Public Broadcasting</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 29.40/hour</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d32d0ebe72ec48c094b3fe6141e40639-digital-audience-and-news-producer-maine-public-broadcasting-portland</t>
+  </si>
+  <si>
+    <t>Dirección Fundadora</t>
+  </si>
+  <si>
+    <t>HRIC Executive Search</t>
+  </si>
+  <si>
+    <t>La Paz, Baja California Sur, MX</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/761f12edfca74060b5569bc5f949f4ad-direccion-fundadora-hric-executive-search-la-paz</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Rainforest Trust</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8688b974a3f64914967f14976587f329-director-of-finance-rainforest-trust-warrenton</t>
+  </si>
+  <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>THE CARE CENTER</t>
+  </si>
+  <si>
+    <t>Holyoke, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd1e5fb58ea940eeb450404de6038a8a-director-of-finance-and-operations-the-care-center-holyoke</t>
+  </si>
+  <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>SEIU 509: The Massachusetts Union for Human Service Workers &amp; Educators</t>
+  </si>
+  <si>
+    <t>Marlborough, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 120372.00 - 127517.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13aed8a56ca646d490926df633da0a5c-director-of-human-resources-seiu-509-the-massachusetts-union-for-human-service-workers-educators-marlborough</t>
+  </si>
+  <si>
+    <t>Director of Policy &amp; Coalition Building</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa5a082e26b2407e8b866e4ba3cb8c54-director-of-policy-coalition-building-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Director, Tax Policy</t>
+  </si>
+  <si>
+    <t>The Bipartisan Policy Center</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Community Development, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd1c0d6d4f0b4ce28b256b2509682768-director-tax-policy-the-bipartisan-policy-center-washington</t>
+  </si>
+  <si>
+    <t>Disability Employment Specialist</t>
+  </si>
+  <si>
+    <t>Job Path, Inc.</t>
+  </si>
+  <si>
+    <t>USD 43600.00 - 45600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8068dd2c4ac4cd3abdec02f74750547-disability-employment-specialist-job-path-inc-new-york</t>
+  </si>
+  <si>
+    <t>Domestic Violence Counselor-Coordinated Safety Response Program</t>
+  </si>
+  <si>
+    <t>RESPOND, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d47f870feb214ed6b03ea4ad33348b20-domestic-violence-counselor-coordinated-safety-response-program-respond-inc-boston</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Temple B'nai Shalom</t>
+  </si>
+  <si>
+    <t>Fairfax Station, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e654564843b64e9b95194931f534f8f6-executive-assistant-temple-bnai-shalom-fairfax-station</t>
+  </si>
+  <si>
+    <t>Framingham History Center</t>
+  </si>
+  <si>
+    <t>Framingham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Arts Music, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb9e725cbf0843c8896b5895084f541e-executive-director-framingham-history-center-framingham</t>
+  </si>
+  <si>
+    <t>Lopez Community Land Trust</t>
+  </si>
+  <si>
+    <t>Lopez Island, Washington</t>
+  </si>
+  <si>
+    <t>USD 117000.00 - 134000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65f89908f10447fbb38747ae21c5a0eb-executive-director-lopez-community-land-trust-lopez-island</t>
+  </si>
+  <si>
+    <t>Financial Reporting Manager</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 119041.00 - 132268.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc98734a85624c51af35ccdf3fd4bba6-financial-reporting-manager-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Full-Time Operations Manager</t>
+  </si>
+  <si>
+    <t>Latinas On the Verge of Excellence - LOVE, Inc</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a67259a27c704ce99fefa96fda3e4b52-full-time-operations-manager-latinas-on-the-verge-of-excellence-love-inc-new-york</t>
+  </si>
+  <si>
+    <t>Fundraising Manager</t>
+  </si>
+  <si>
+    <t>ARTISTIC VOICES INC</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 400.00 - 400.00/month</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38409a4141b14bccbc45d986f819e5d0-fundraising-manager-artistic-voices-inc-miami</t>
+  </si>
+  <si>
+    <t>Graphic &amp; Multimedia Coordinator</t>
+  </si>
+  <si>
+    <t>Child's Dream Foundation</t>
+  </si>
+  <si>
+    <t>Chiang Mai, (no state), TH</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66718243a71c49e38eb8f6ab2da70d4f-graphic-multimedia-coordinator-childs-dream-foundation-chiang-mai</t>
+  </si>
+  <si>
+    <t>Home Tutors – Hyderabad &amp; Telangana</t>
+  </si>
+  <si>
+    <t>Shiva's Tutorial</t>
+  </si>
+  <si>
+    <t>Hyderabad, Telangana, IN</t>
+  </si>
+  <si>
+    <t>USD 5.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3f2f8ce6359480db8e48cc2cf7f44fa-home-tutors-hyderabad-telangana-shivas-tutorial-hyderabad</t>
+  </si>
+  <si>
+    <t>Interim/Permanent Traditional Worship Accompanist (Organ &amp; Piano)</t>
+  </si>
+  <si>
+    <t>New Providence Presbyterian Church</t>
+  </si>
+  <si>
+    <t>New Providence, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afed028d05554a12ab0822eee1c0cd2a-interimpermanent-traditional-worship-accompanist-organ-piano-new-providence-presbyterian-church-new-providence</t>
+  </si>
+  <si>
+    <t>Interim/Permanent Traditional Worship Director (Choir &amp; Handbells)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f50465b37d2445f97e6ed492e435cce-interimpermanent-traditional-worship-director-choir-handbells-new-providence-presbyterian-church-new-providence</t>
+  </si>
+  <si>
+    <t>Labor Representative</t>
+  </si>
+  <si>
+    <t>USD 78412.29/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f45f6968cb4d4d96ae89c7492dbb4f23-labor-representative-ohio-nurses-association-columbus</t>
+  </si>
+  <si>
+    <t>Learning and Impact Manager</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eaeade1ec6494244b1df97c9b8fc9a7b-learning-and-impact-manager-multiplier-san-francisco</t>
+  </si>
+  <si>
+    <t>Manager of Grants and Project Support</t>
+  </si>
+  <si>
+    <t>The Hastings Center</t>
+  </si>
+  <si>
+    <t>Garrison, NY</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d9f5c2e1a0f4784a18d245a9d1bce25-manager-of-grants-and-project-support-the-hastings-center-garrison</t>
+  </si>
+  <si>
+    <t>Medical Assistant Lead Teacher</t>
+  </si>
+  <si>
+    <t>Briya Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 68299.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c8140ca8b684cd68379c0b06304ffe1-medical-assistant-lead-teacher-briya-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>Membership Retention Specialist</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>Martinsburg, West Virginia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/847bf3d47b294540a16276be63e89107-membership-retention-specialist-girl-scout-council-of-the-nations-capital-martinsburg</t>
+  </si>
+  <si>
+    <t>Mental Health Rehabilitation Counselor - Full Time</t>
+  </si>
+  <si>
+    <t>Southern Tier Environments for Living, Inc.</t>
+  </si>
+  <si>
+    <t>Gowanda, New York</t>
+  </si>
+  <si>
+    <t>USD 19.57 - 19.57/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a475c63497104ccca45f71b531f9c7c6-mental-health-rehabilitation-counselor-full-time-southern-tier-environments-for-living-inc-gowanda</t>
+  </si>
+  <si>
+    <t>Nonprofit Mobilization Coordinator</t>
+  </si>
+  <si>
+    <t>REBUILD LOCAL NEWS</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a4061442ee19424aa90003525ddace56-nonprofit-mobilization-coordinator-rebuild-local-news-brooklyn</t>
+  </si>
+  <si>
+    <t>PaintCare Program Coordinator for New York</t>
+  </si>
+  <si>
+    <t>PaintCare &amp; American Coatings Association</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/075b6bd18fd646fea0dce4adbd2baf92-paintcare-program-coordinator-for-new-york-paintcare-american-coatings-association-buffalo</t>
+  </si>
+  <si>
+    <t>PaintCare Public Relations Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/255c0546655d494db4c5ffbc62d6b2ce-paintcare-public-relations-manager-paintcare-american-coatings-association-washington</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 67793.00 - 72442.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1f920df3a82420facfc0c85665b0a2f-paralegal-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Operations Associate</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/902ca83c89a74b6ea30004fbf87f2658-part-time-operations-associate-latinas-on-the-verge-of-excellence-love-inc-new-york</t>
+  </si>
+  <si>
+    <t>PBHA Program Support Fellow</t>
+  </si>
+  <si>
+    <t>Volunteering, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b47d8fecf2be43129e609791a9c9674e-pbha-program-support-fellow-phillips-brooks-house-association-cambridge</t>
+  </si>
+  <si>
+    <t>Peninsula Program Manager - Coastside</t>
+  </si>
+  <si>
+    <t>Renaissance Entrepreneurship Center</t>
+  </si>
+  <si>
+    <t>Half Moon Bay, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/580470ac2fa94707b4acc4b28c720b0a-peninsula-program-manager-coastside-renaissance-entrepreneurship-center-half-moon-bay</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Hughes Memorial Union</t>
+  </si>
+  <si>
+    <t>Cornwall, Connecticut</t>
+  </si>
+  <si>
+    <t>Agriculture, Arts Music, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82504249431c4514bc051a8d70b067ca-program-manager-hughes-memorial-union-cornwall</t>
+  </si>
+  <si>
+    <t>Programs Coordinator - Full Time - Remote</t>
+  </si>
+  <si>
+    <t>Mary's Meals USA</t>
+  </si>
+  <si>
+    <t>Education, International Relations, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/598667dece8a446ba4788598f96dc28d-programs-coordinator-full-time-remote-marys-meals-usa-bloomfield</t>
+  </si>
+  <si>
+    <t>Research and Strategic Initiatives Manager</t>
+  </si>
+  <si>
+    <t>American Association for State and Local History (AASLH)</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d9c884871aa436aa8972cf02fd3d74a-research-and-strategic-initiatives-manager-american-association-for-state-and-local-history-aaslh-nashville</t>
+  </si>
+  <si>
+    <t>Residential Case Manager</t>
+  </si>
+  <si>
+    <t>Child Abuse Prevention Association, CAPA</t>
+  </si>
+  <si>
+    <t>Port Royal, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 54080.00 - 54080.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54e90ab0d85e455195e2e24c222a2827-residential-case-manager-child-abuse-prevention-association-capa-port-royal</t>
+  </si>
+  <si>
+    <t>SARE Grant Program Admin - Partnership Grant</t>
+  </si>
+  <si>
+    <t>University of Vermont</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5aa0051865914716a0a380094301febb-sare-grant-program-admin-partnership-grant-university-of-vermont-burlington</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Institute for Energy Economics and Financial Analysis</t>
+  </si>
+  <si>
+    <t>USD 84228.00 - 101652.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98eed4fc5d424eecaa5c45afcb5c1666-senior-accountant-institute-for-energy-economics-and-financial-analysis-lakewood</t>
+  </si>
+  <si>
+    <t>Senior Advisor, Vaccine &amp; Clinical Case Management</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>USD 91520.00 - 151840.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/a2039f5f3fa84c48abf770f6a3776483-senior-advisor-vaccine-clinical-case-management-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Senior Associate, Jewish Communal Engagement</t>
+  </si>
+  <si>
+    <t>J Street</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a78e069f8064d5e9436e1154c467f8a-senior-associate-jewish-communal-engagement-j-street-new-york</t>
+  </si>
+  <si>
+    <t>Senior Associate, Portfolio Management</t>
+  </si>
+  <si>
+    <t>RSF Social Finance</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17cbafb3bd8a44b084ef912b40671fc5-senior-associate-portfolio-management-rsf-social-finance-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Director - Management and Administration</t>
+  </si>
+  <si>
+    <t>Center Theatre Group via TOC Arts Partners</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c2ab4dc9053342c2bf5efed6c2161d37-senior-director-management-and-administration-center-theatre-group-via-toc-arts-partners-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>American Museum Of Natural History</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0e103068f03c47a5b2226dfd363fecbc-senior-major-gifts-officer-american-museum-of-natural-history-new-york</t>
+  </si>
+  <si>
+    <t>Site Manager</t>
+  </si>
+  <si>
+    <t>GiGi's Playhouse Hillsborough</t>
+  </si>
+  <si>
+    <t>Hillsborough Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02ef85ba262142ad9b99b60faf1ec75c-site-manager-gigis-playhouse-hillsborough-hillsborough-township</t>
+  </si>
+  <si>
+    <t>Staff Associate I</t>
+  </si>
+  <si>
+    <t>Incite Institute at Columbia University</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f94d7a0d4664cf29573b7edbd3b1ea5-staff-associate-i-incite-institute-at-columbia-university-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Greater Boston Legal Services</t>
+  </si>
+  <si>
+    <t>USD 79500.00 - 85500.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93f02804efda4a19a1de12ab9dd70bbc-staff-attorney-greater-boston-legal-services-boston</t>
+  </si>
+  <si>
+    <t>USD 90262.00 - 96436.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3850249574cb4d78b9da201ac83b5ccd-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Student Support Counselor</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 68500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5244d5cf406447c2bf82706ec3a53dcd-student-support-counselor-the-care-center-holyoke</t>
+  </si>
+  <si>
+    <t>Supervising Immigration Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80c8322f074b4816a038147c27fe119b-supervising-immigration-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Supported Employment Counselor</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5746180c2e404f9aadc0085663e2dcc2-supported-employment-counselor-job-path-inc-new-york</t>
+  </si>
+  <si>
+    <t>Temporary Paralegal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6db6346534d348d581c8d27fb7143df4-temporary-paralegal-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Trauma Therapist - Full-Time - Counseling Center</t>
+  </si>
+  <si>
+    <t>USD 29.67 - 32.69/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdc3bf093a004b39bf39411f23991306-trauma-therapist-full-time-counseling-center-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Undercover Investigator</t>
+  </si>
+  <si>
+    <t>Animal Equality</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64c6e2925bde4311be033ec456d6ecdc-undercover-investigator-animal-equality-los-angeles</t>
+  </si>
+  <si>
+    <t>Undercover Investigator, Germany</t>
+  </si>
+  <si>
+    <t>Remote (DE)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4963ba2267ad48db918e2c5e19896e7c-undercover-investigator-germany-animal-equality-los-angeles</t>
+  </si>
+  <si>
+    <t>Writing Instructor</t>
+  </si>
+  <si>
+    <t>Legal Outreach</t>
+  </si>
+  <si>
+    <t>Long Is City, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3895ee8a359e45f29a2655408e8c0453-writing-instructor-legal-outreach-long-is-city</t>
+  </si>
+  <si>
     <t>AGENCY RELATIONS COORDINATOR</t>
   </si>
   <si>
@@ -49,9 +1615,6 @@
     <t>Seattle, Washington</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Program Operations</t>
   </si>
   <si>
@@ -221,9 +1784,6 @@
   </si>
   <si>
     <t>Tilth Alliance</t>
-  </si>
-  <si>
-    <t>Executive Director</t>
   </si>
   <si>
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73951453</t>
@@ -879,7 +2439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -918,8 +2478,562 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -927,7 +3041,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -966,8 +3080,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -975,7 +3115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1014,8 +3154,1906 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" t="s">
+        <v>187</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" t="s">
+        <v>202</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" t="s">
+        <v>212</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F15" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" t="s">
+        <v>225</v>
+      </c>
+      <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" t="s">
+        <v>234</v>
+      </c>
+      <c r="D18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" t="s">
+        <v>235</v>
+      </c>
+      <c r="F18" t="s">
+        <v>236</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" t="s">
+        <v>247</v>
+      </c>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" t="s">
+        <v>248</v>
+      </c>
+      <c r="F20" t="s">
+        <v>249</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" t="s">
+        <v>253</v>
+      </c>
+      <c r="F21" t="s">
+        <v>254</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F22" t="s">
+        <v>260</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" t="s">
+        <v>263</v>
+      </c>
+      <c r="C23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" t="s">
+        <v>265</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" t="s">
+        <v>270</v>
+      </c>
+      <c r="F24" t="s">
+        <v>271</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>273</v>
+      </c>
+      <c r="B25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" t="s">
+        <v>277</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>279</v>
+      </c>
+      <c r="B26" t="s">
+        <v>280</v>
+      </c>
+      <c r="C26" t="s">
+        <v>281</v>
+      </c>
+      <c r="D26" t="s">
+        <v>152</v>
+      </c>
+      <c r="E26" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" t="s">
+        <v>283</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>285</v>
+      </c>
+      <c r="B27" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" t="s">
+        <v>287</v>
+      </c>
+      <c r="D27" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>288</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>290</v>
+      </c>
+      <c r="B28" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" t="s">
+        <v>292</v>
+      </c>
+      <c r="F28" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>295</v>
+      </c>
+      <c r="B29" t="s">
+        <v>296</v>
+      </c>
+      <c r="C29" t="s">
+        <v>297</v>
+      </c>
+      <c r="D29" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" t="s">
+        <v>212</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>300</v>
+      </c>
+      <c r="B30" t="s">
+        <v>301</v>
+      </c>
+      <c r="C30" t="s">
+        <v>302</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" t="s">
+        <v>304</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31" t="s">
+        <v>307</v>
+      </c>
+      <c r="C31" t="s">
+        <v>308</v>
+      </c>
+      <c r="D31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" t="s">
+        <v>309</v>
+      </c>
+      <c r="F31" t="s">
+        <v>310</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B32" t="s">
+        <v>313</v>
+      </c>
+      <c r="C32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" t="s">
+        <v>315</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C33" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" t="s">
+        <v>319</v>
+      </c>
+      <c r="F33" t="s">
+        <v>146</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" t="s">
+        <v>323</v>
+      </c>
+      <c r="D34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34" t="s">
+        <v>324</v>
+      </c>
+      <c r="F34" t="s">
+        <v>325</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" t="s">
+        <v>328</v>
+      </c>
+      <c r="C35" t="s">
+        <v>329</v>
+      </c>
+      <c r="D35" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" t="s">
+        <v>330</v>
+      </c>
+      <c r="F35" t="s">
+        <v>331</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" t="s">
+        <v>334</v>
+      </c>
+      <c r="D36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" t="s">
+        <v>335</v>
+      </c>
+      <c r="F36" t="s">
+        <v>336</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>338</v>
+      </c>
+      <c r="C37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D37" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" t="s">
+        <v>340</v>
+      </c>
+      <c r="F37" t="s">
+        <v>341</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>343</v>
+      </c>
+      <c r="B38" t="s">
+        <v>344</v>
+      </c>
+      <c r="C38" t="s">
+        <v>345</v>
+      </c>
+      <c r="D38" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" t="s">
+        <v>346</v>
+      </c>
+      <c r="F38" t="s">
+        <v>347</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>349</v>
+      </c>
+      <c r="B39" t="s">
+        <v>350</v>
+      </c>
+      <c r="C39" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" t="s">
+        <v>351</v>
+      </c>
+      <c r="F39" t="s">
+        <v>260</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>353</v>
+      </c>
+      <c r="B40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" t="s">
+        <v>355</v>
+      </c>
+      <c r="E40" t="s">
+        <v>356</v>
+      </c>
+      <c r="F40" t="s">
+        <v>357</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>359</v>
+      </c>
+      <c r="B41" t="s">
+        <v>360</v>
+      </c>
+      <c r="C41" t="s">
+        <v>361</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>363</v>
+      </c>
+      <c r="B42" t="s">
+        <v>364</v>
+      </c>
+      <c r="C42" t="s">
+        <v>365</v>
+      </c>
+      <c r="D42" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" t="s">
+        <v>366</v>
+      </c>
+      <c r="F42" t="s">
+        <v>367</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>369</v>
+      </c>
+      <c r="B43" t="s">
+        <v>370</v>
+      </c>
+      <c r="C43" t="s">
+        <v>371</v>
+      </c>
+      <c r="D43" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" t="s">
+        <v>373</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B44" t="s">
+        <v>370</v>
+      </c>
+      <c r="C44" t="s">
+        <v>371</v>
+      </c>
+      <c r="D44" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" t="s">
+        <v>372</v>
+      </c>
+      <c r="F44" t="s">
+        <v>373</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>377</v>
+      </c>
+      <c r="B45" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" t="s">
+        <v>378</v>
+      </c>
+      <c r="F45" t="s">
+        <v>265</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>380</v>
+      </c>
+      <c r="B46" t="s">
+        <v>381</v>
+      </c>
+      <c r="C46" t="s">
+        <v>247</v>
+      </c>
+      <c r="D46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E46" t="s">
+        <v>382</v>
+      </c>
+      <c r="F46" t="s">
+        <v>383</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>385</v>
+      </c>
+      <c r="B47" t="s">
+        <v>386</v>
+      </c>
+      <c r="C47" t="s">
+        <v>387</v>
+      </c>
+      <c r="D47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" t="s">
+        <v>388</v>
+      </c>
+      <c r="F47" t="s">
+        <v>389</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>391</v>
+      </c>
+      <c r="B48" t="s">
+        <v>392</v>
+      </c>
+      <c r="C48" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" t="s">
+        <v>393</v>
+      </c>
+      <c r="F48" t="s">
+        <v>394</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>396</v>
+      </c>
+      <c r="B49" t="s">
+        <v>397</v>
+      </c>
+      <c r="C49" t="s">
+        <v>398</v>
+      </c>
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" t="s">
+        <v>399</v>
+      </c>
+      <c r="F49" t="s">
+        <v>400</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>402</v>
+      </c>
+      <c r="B50" t="s">
+        <v>403</v>
+      </c>
+      <c r="C50" t="s">
+        <v>404</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" t="s">
+        <v>405</v>
+      </c>
+      <c r="F50" t="s">
+        <v>406</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>408</v>
+      </c>
+      <c r="B51" t="s">
+        <v>409</v>
+      </c>
+      <c r="C51" t="s">
+        <v>247</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" t="s">
+        <v>388</v>
+      </c>
+      <c r="F51" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>411</v>
+      </c>
+      <c r="B52" t="s">
+        <v>412</v>
+      </c>
+      <c r="C52" t="s">
+        <v>413</v>
+      </c>
+      <c r="D52" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" t="s">
+        <v>351</v>
+      </c>
+      <c r="F52" t="s">
+        <v>414</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>416</v>
+      </c>
+      <c r="B53" t="s">
+        <v>412</v>
+      </c>
+      <c r="C53" t="s">
+        <v>219</v>
+      </c>
+      <c r="D53" t="s">
+        <v>152</v>
+      </c>
+      <c r="E53" t="s">
+        <v>248</v>
+      </c>
+      <c r="F53" t="s">
+        <v>414</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>418</v>
+      </c>
+      <c r="B54" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" t="s">
+        <v>185</v>
+      </c>
+      <c r="D54" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" t="s">
+        <v>420</v>
+      </c>
+      <c r="F54" t="s">
+        <v>310</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>422</v>
+      </c>
+      <c r="B55" t="s">
+        <v>350</v>
+      </c>
+      <c r="C55" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" t="s">
+        <v>355</v>
+      </c>
+      <c r="E55" t="s">
+        <v>423</v>
+      </c>
+      <c r="F55" t="s">
+        <v>260</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>425</v>
+      </c>
+      <c r="B56" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" t="s">
+        <v>179</v>
+      </c>
+      <c r="D56" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" t="s">
+        <v>426</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>428</v>
+      </c>
+      <c r="B57" t="s">
+        <v>429</v>
+      </c>
+      <c r="C57" t="s">
+        <v>430</v>
+      </c>
+      <c r="D57" t="s">
+        <v>152</v>
+      </c>
+      <c r="E57" t="s">
+        <v>431</v>
+      </c>
+      <c r="F57" t="s">
+        <v>432</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>434</v>
+      </c>
+      <c r="B58" t="s">
+        <v>435</v>
+      </c>
+      <c r="C58" t="s">
+        <v>436</v>
+      </c>
+      <c r="D58" t="s">
+        <v>355</v>
+      </c>
+      <c r="E58" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" t="s">
+        <v>437</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>439</v>
+      </c>
+      <c r="B59" t="s">
+        <v>440</v>
+      </c>
+      <c r="C59" t="s">
+        <v>247</v>
+      </c>
+      <c r="D59" t="s">
+        <v>152</v>
+      </c>
+      <c r="E59" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" t="s">
+        <v>441</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>443</v>
+      </c>
+      <c r="B60" t="s">
+        <v>444</v>
+      </c>
+      <c r="C60" t="s">
+        <v>247</v>
+      </c>
+      <c r="D60" t="s">
+        <v>152</v>
+      </c>
+      <c r="E60" t="s">
+        <v>445</v>
+      </c>
+      <c r="F60" t="s">
+        <v>146</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>447</v>
+      </c>
+      <c r="B61" t="s">
+        <v>448</v>
+      </c>
+      <c r="C61" t="s">
+        <v>449</v>
+      </c>
+      <c r="D61" t="s">
+        <v>152</v>
+      </c>
+      <c r="E61" t="s">
+        <v>450</v>
+      </c>
+      <c r="F61" t="s">
+        <v>451</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>453</v>
+      </c>
+      <c r="B62" t="s">
+        <v>454</v>
+      </c>
+      <c r="C62" t="s">
+        <v>455</v>
+      </c>
+      <c r="D62" t="s">
+        <v>152</v>
+      </c>
+      <c r="E62" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" t="s">
+        <v>146</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>457</v>
+      </c>
+      <c r="B63" t="s">
+        <v>458</v>
+      </c>
+      <c r="C63" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" t="s">
+        <v>152</v>
+      </c>
+      <c r="E63" t="s">
+        <v>459</v>
+      </c>
+      <c r="F63" t="s">
+        <v>460</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>462</v>
+      </c>
+      <c r="B64" t="s">
+        <v>463</v>
+      </c>
+      <c r="C64" t="s">
+        <v>247</v>
+      </c>
+      <c r="D64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E64" t="s">
+        <v>464</v>
+      </c>
+      <c r="F64" t="s">
+        <v>265</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>466</v>
+      </c>
+      <c r="B65" t="s">
+        <v>467</v>
+      </c>
+      <c r="C65" t="s">
+        <v>185</v>
+      </c>
+      <c r="D65" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" t="s">
+        <v>468</v>
+      </c>
+      <c r="F65" t="s">
+        <v>469</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>471</v>
+      </c>
+      <c r="B66" t="s">
+        <v>472</v>
+      </c>
+      <c r="C66" t="s">
+        <v>247</v>
+      </c>
+      <c r="D66" t="s">
+        <v>152</v>
+      </c>
+      <c r="E66" t="s">
+        <v>473</v>
+      </c>
+      <c r="F66" t="s">
+        <v>474</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>476</v>
+      </c>
+      <c r="B67" t="s">
+        <v>477</v>
+      </c>
+      <c r="C67" t="s">
+        <v>478</v>
+      </c>
+      <c r="D67" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" t="s">
+        <v>479</v>
+      </c>
+      <c r="F67" t="s">
+        <v>480</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>482</v>
+      </c>
+      <c r="B68" t="s">
+        <v>483</v>
+      </c>
+      <c r="C68" t="s">
+        <v>185</v>
+      </c>
+      <c r="D68" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" t="s">
+        <v>146</v>
+      </c>
+      <c r="F68" t="s">
+        <v>146</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>485</v>
+      </c>
+      <c r="B69" t="s">
+        <v>486</v>
+      </c>
+      <c r="C69" t="s">
+        <v>487</v>
+      </c>
+      <c r="D69" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" t="s">
+        <v>488</v>
+      </c>
+      <c r="F69" t="s">
+        <v>489</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>491</v>
+      </c>
+      <c r="B70" t="s">
+        <v>492</v>
+      </c>
+      <c r="C70" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" t="s">
+        <v>152</v>
+      </c>
+      <c r="E70" t="s">
+        <v>493</v>
+      </c>
+      <c r="F70" t="s">
+        <v>146</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>495</v>
+      </c>
+      <c r="B71" t="s">
+        <v>496</v>
+      </c>
+      <c r="C71" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" t="s">
+        <v>152</v>
+      </c>
+      <c r="E71" t="s">
+        <v>497</v>
+      </c>
+      <c r="F71" t="s">
+        <v>498</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>495</v>
+      </c>
+      <c r="B72" t="s">
+        <v>419</v>
+      </c>
+      <c r="C72" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" t="s">
+        <v>152</v>
+      </c>
+      <c r="E72" t="s">
+        <v>500</v>
+      </c>
+      <c r="F72" t="s">
+        <v>310</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>502</v>
+      </c>
+      <c r="B73" t="s">
+        <v>296</v>
+      </c>
+      <c r="C73" t="s">
+        <v>297</v>
+      </c>
+      <c r="D73" t="s">
+        <v>152</v>
+      </c>
+      <c r="E73" t="s">
+        <v>503</v>
+      </c>
+      <c r="F73" t="s">
+        <v>212</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>505</v>
+      </c>
+      <c r="B74" t="s">
+        <v>419</v>
+      </c>
+      <c r="C74" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" t="s">
+        <v>152</v>
+      </c>
+      <c r="E74" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" t="s">
+        <v>310</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>507</v>
+      </c>
+      <c r="B75" t="s">
+        <v>318</v>
+      </c>
+      <c r="C75" t="s">
+        <v>185</v>
+      </c>
+      <c r="D75" t="s">
+        <v>152</v>
+      </c>
+      <c r="E75" t="s">
+        <v>319</v>
+      </c>
+      <c r="F75" t="s">
+        <v>508</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>510</v>
+      </c>
+      <c r="B76" t="s">
+        <v>419</v>
+      </c>
+      <c r="C76" t="s">
+        <v>185</v>
+      </c>
+      <c r="D76" t="s">
+        <v>152</v>
+      </c>
+      <c r="E76" t="s">
+        <v>420</v>
+      </c>
+      <c r="F76" t="s">
+        <v>310</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>512</v>
+      </c>
+      <c r="B77" t="s">
+        <v>224</v>
+      </c>
+      <c r="C77" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77" t="s">
+        <v>152</v>
+      </c>
+      <c r="E77" t="s">
+        <v>513</v>
+      </c>
+      <c r="F77" t="s">
+        <v>226</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>515</v>
+      </c>
+      <c r="B78" t="s">
+        <v>516</v>
+      </c>
+      <c r="C78" t="s">
+        <v>247</v>
+      </c>
+      <c r="D78" t="s">
+        <v>152</v>
+      </c>
+      <c r="E78" t="s">
+        <v>517</v>
+      </c>
+      <c r="F78" t="s">
+        <v>518</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>520</v>
+      </c>
+      <c r="B79" t="s">
+        <v>516</v>
+      </c>
+      <c r="C79" t="s">
+        <v>521</v>
+      </c>
+      <c r="D79" t="s">
+        <v>241</v>
+      </c>
+      <c r="E79" t="s">
+        <v>146</v>
+      </c>
+      <c r="F79" t="s">
+        <v>518</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>523</v>
+      </c>
+      <c r="B80" t="s">
+        <v>524</v>
+      </c>
+      <c r="C80" t="s">
+        <v>525</v>
+      </c>
+      <c r="D80" t="s">
+        <v>526</v>
+      </c>
+      <c r="E80" t="s">
+        <v>527</v>
+      </c>
+      <c r="F80" t="s">
+        <v>528</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1064,1014 +5102,1014 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>530</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>531</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>532</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>534</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>535</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>536</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>537</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>539</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>540</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>541</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>542</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>544</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>545</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>546</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>548</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>549</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>550</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>552</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>553</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>554</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>555</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>557</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>558</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>559</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>560</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>562</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>563</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>44</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>566</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>567</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>568</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>48</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>570</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>571</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>572</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>560</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>52</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>574</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>567</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>568</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>54</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>577</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>578</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>58</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>577</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>578</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>59</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>581</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>545</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>546</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>582</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>584</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>585</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>554</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>66</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>588</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>589</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>532</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>70</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>591</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>592</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>554</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>542</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>594</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>595</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>596</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>77</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>599</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>81</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>603</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>604</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>85</v>
+        <v>605</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>606</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>607</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>608</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>582</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>89</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>610</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>611</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>612</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>93</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>614</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>571</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>572</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>95</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>616</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>617</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>618</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>99</v>
+        <v>619</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>620</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>621</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>622</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>103</v>
+        <v>623</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>624</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>567</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>568</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>105</v>
+        <v>625</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>626</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>563</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>107</v>
+        <v>627</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>628</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>629</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>630</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>111</v>
+        <v>631</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>632</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>563</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>564</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>113</v>
+        <v>633</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>634</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>545</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>546</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>115</v>
+        <v>635</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>634</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>545</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>546</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>116</v>
+        <v>636</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>637</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>638</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>639</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>120</v>
+        <v>640</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>641</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>642</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>643</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>124</v>
+        <v>644</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>645</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>646</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>647</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>582</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>128</v>
+        <v>648</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>649</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>650</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>651</v>
       </c>
       <c r="D36" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>132</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>653</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>654</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>655</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>560</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>136</v>
+        <v>656</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>657</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>638</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>639</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>138</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>659</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>660</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>661</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>142</v>
+        <v>662</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>663</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>664</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>665</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>560</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>146</v>
+        <v>666</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>667</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>668</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>572</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>149</v>
+        <v>669</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>670</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>654</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>655</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F42" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>151</v>
+        <v>671</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>672</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>660</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>673</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>154</v>
+        <v>674</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>675</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>638</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>639</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>156</v>
+        <v>676</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>677</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>678</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>673</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>159</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>

--- a/docs/xlsx/jobs-2026-10-14.xlsx
+++ b/docs/xlsx/jobs-2026-10-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="904">
   <si>
     <t>Title</t>
   </si>
@@ -463,6 +463,27 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/public-affairs-intern-8/</t>
   </si>
   <si>
+    <t>A/P Clerk</t>
+  </si>
+  <si>
+    <t>Seva Foundation</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7f64a309d184c03b4589c7b4ec1232a-ap-clerk-seva-foundation-berkeley</t>
+  </si>
+  <si>
     <t>Administrative Assistant/Accounts Payable</t>
   </si>
   <si>
@@ -547,6 +568,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8ebf6662e7d940b6a5146c67c56a5c3c-advancement-coordinator-society-of-fellows-the-huntington-library-art-museum-and-botanical-gardens-san-marino</t>
   </si>
   <si>
+    <t>Annual Fund &amp; Events Manager</t>
+  </si>
+  <si>
+    <t>Planned Parenthood of Western Pennsylvania</t>
+  </si>
+  <si>
+    <t>Pittsburgh, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/595b32ea7d794926a795c62fd8f49ea8-annual-fund-events-manager-planned-parenthood-of-western-pennsylvania-pittsburgh</t>
+  </si>
+  <si>
     <t>Assistant Director of Operations and Development</t>
   </si>
   <si>
@@ -565,6 +604,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ed833e77c6b14f66b34dbfb35e216c85-assistant-director-of-operations-and-development-phillips-brooks-house-association-cambridge</t>
   </si>
   <si>
+    <t>Assistant Director, Career Development</t>
+  </si>
+  <si>
+    <t>Loyola Marymount University</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 72900.00 - 91100.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57e16688c989463f8209126007c1f37c-assistant-director-career-development-loyola-marymount-university-los-angeles</t>
+  </si>
+  <si>
     <t>Assistant Director, CRM Special Projects</t>
   </si>
   <si>
@@ -640,6 +697,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/ba63129d31a14b60b49fe44b0e20dde3-associate-managing-director-hadassah-wzoa-inc-boynton-beach</t>
   </si>
   <si>
+    <t>Associate Teacher (K-5)</t>
+  </si>
+  <si>
+    <t>Harlem Academy</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3364163ebd924403a87a1a0f9f04682c-associate-teacher-k-5-harlem-academy-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Youth Mentor</t>
+  </si>
+  <si>
+    <t>A. Marie Consultants</t>
+  </si>
+  <si>
+    <t>Montgomery County, Maryland</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/77c201b64db24ce7845040906dfcec74-bilingual-youth-mentor-a-marie-consultants-montgomery-county</t>
+  </si>
+  <si>
+    <t>Billing &amp; Legal Assistant (full-time) at Law Firm Exclusively Serving Nonproﬁt/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/f6ae75fa833b4972965fa6d27b54ffdc-billing-legal-assistant-full-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
     <t>Certified Middle School Math Teacher CT SY26-27</t>
   </si>
   <si>
@@ -652,9 +760,6 @@
     <t>USD 53235.00 - 118163.00/year</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/031c332c5dbc41b7b8e5c736ebd62557-certified-middle-school-math-teacher-ct-sy26-27-excellence-community-schools-stamford</t>
   </si>
   <si>
@@ -685,6 +790,21 @@
     <t>https://www.idealist.org/en/job/f6956bc465654228aaebba7d95640558-chief-financial-officer-daughters-of-the-american-revolution-washington</t>
   </si>
   <si>
+    <t>Scouting America, Circle Ten Council</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>USD 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62690ba5d1c14ef798891ede2e56aec3-chief-financial-officer-scouting-america-circle-ten-council-dallas</t>
+  </si>
+  <si>
     <t>Child Trauma Responder CTRT - HYBRID schedule</t>
   </si>
   <si>
@@ -700,6 +820,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/b7371be190ea4b81807204b1ae9d8543-child-trauma-responder-ctrt-hybrid-schedule-safe-horizon-new-york</t>
   </si>
   <si>
+    <t>Children, Youth &amp; Family Minister</t>
+  </si>
+  <si>
+    <t>St. John's Episcopal Church, Bangor, Maine</t>
+  </si>
+  <si>
+    <t>Bangor, Maine</t>
+  </si>
+  <si>
+    <t>USD 15000.00 - 15000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57d58ec71d9a4a129fee95634c09a975-children-youth-family-minister-st-johns-episcopal-church-bangor-maine-bangor</t>
+  </si>
+  <si>
+    <t>Clinical Assistant Professor - Counseling for Mental Health and Wellness MA Program, Non-Tenure Track</t>
+  </si>
+  <si>
+    <t>New York University Steinhardt School of Culture, Education, and Human Development</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7b300fe48734eb98558e8aea1b21a65-clinical-assistant-professor-counseling-for-mental-health-and-wellness-ma-program-non-tenure-track-new-york-university-steinhardt-school-of-culture-education-and-human-development-new-york</t>
+  </si>
+  <si>
+    <t>Clinical Nurse Consultant</t>
+  </si>
+  <si>
+    <t>Cardea Services</t>
+  </si>
+  <si>
+    <t>Remote (Texas)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 75.00 - 75.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Race Ethnicity, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b97302d2c9145a9846703d755b6d930-clinical-nurse-consultant-cardea-services-austin</t>
+  </si>
+  <si>
+    <t>Communications and Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Engage Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57300.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed17800ea9694e97bffe8ee7d22b3758-communications-and-operations-coordinator-engage-chicago-chicago</t>
+  </si>
+  <si>
     <t>Communications Operations Manager</t>
   </si>
   <si>
@@ -730,6 +919,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/cb175e2dc77e4e468c6f6810a4f5ee3a-community-first-senior-replication-manager-mobile-loaves-fishes-austin</t>
   </si>
   <si>
+    <t>Community Life Associate / Community Life Minister</t>
+  </si>
+  <si>
+    <t>St. Andrew's Episcopal Church, Yardley</t>
+  </si>
+  <si>
+    <t>Yardley, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8dbfc0a3fb34fe9a7fc3ca8ceacf01c-community-life-associate-community-life-minister-st-andrews-episcopal-church-yardley-yardley</t>
+  </si>
+  <si>
+    <t>Community Partnerships Associate</t>
+  </si>
+  <si>
+    <t>F.B. Heron Foundation</t>
+  </si>
+  <si>
+    <t>Birmingham, Alabama</t>
+  </si>
+  <si>
+    <t>USD 78500.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5149cded96024a7cbb9363011f85261c-community-partnerships-associate-fb-heron-foundation-birmingham</t>
+  </si>
+  <si>
+    <t>Contabilidad y Finanzas</t>
+  </si>
+  <si>
+    <t>Fundación Sertull A.C.</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 32000.00/month</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a880aa646e6f4831aa021ec6d0779f14-contabilidad-y-finanzas-fundacion-sertull-ac-ciudad-de-mexico</t>
+  </si>
+  <si>
     <t>Contract Lobbyist</t>
   </si>
   <si>
@@ -739,9 +982,6 @@
     <t>Saint Paul, Minnesota</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 40000.00 - 40000.00/year</t>
   </si>
   <si>
@@ -811,9 +1051,6 @@
     <t>Columbus, Ohio</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/904d9162e05746c5877ad1b108d14047-deputy-director-of-organizing-ohio-nurses-association-columbus</t>
   </si>
   <si>
@@ -835,6 +1072,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/876e24f27bb94689bf7d67d46bf7f54f-development-director-sarasota-housing-funding-corp-sarasota</t>
   </si>
   <si>
+    <t>Pennsylvania Prison Society</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Prison Reform, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09de19ac3afe4c6ca44325cb03cca636-development-director-pennsylvania-prison-society-philadelphia</t>
+  </si>
+  <si>
     <t>Development Officer - Major Gifts</t>
   </si>
   <si>
@@ -886,6 +1135,42 @@
     <t>https://www.idealist.org/en/consultant-job/761f12edfca74060b5569bc5f949f4ad-direccion-fundadora-hric-executive-search-la-paz</t>
   </si>
   <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Humane Society of Vero Beach</t>
+  </si>
+  <si>
+    <t>Vero Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/aa8f15ce83d24860bed78c84747d90a7-director-of-development-humane-society-of-vero-beach-vero-beach</t>
+  </si>
+  <si>
+    <t>Director of Discipleship</t>
+  </si>
+  <si>
+    <t>Tuckahoe Presbyterian Church</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16a52503bfef459294ea4201e16bdf59-director-of-discipleship-tuckahoe-presbyterian-church-richmond</t>
+  </si>
+  <si>
     <t>Director of Finance</t>
   </si>
   <si>
@@ -916,6 +1201,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/dd1e5fb58ea940eeb450404de6038a8a-director-of-finance-and-operations-the-care-center-holyoke</t>
   </si>
   <si>
+    <t>Director of Finance, Care in Action</t>
+  </si>
+  <si>
+    <t>National Domestic Workers Alliance / La Alianza Nacional de Trabajadores del Hogar</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec7e0449c7ff4bcda8d9c21d2413d2ae-director-of-finance-care-in-action-national-domestic-workers-alliance-la-alianza-nacional-de-trabajadores-del-hogar-new-york</t>
+  </si>
+  <si>
     <t>Director of Human Resources</t>
   </si>
   <si>
@@ -934,6 +1231,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/13aed8a56ca646d490926df633da0a5c-director-of-human-resources-seiu-509-the-massachusetts-union-for-human-service-workers-educators-marlborough</t>
   </si>
   <si>
+    <t>Director of Operations &amp; Partnerships (COO Equivalent)</t>
+  </si>
+  <si>
+    <t>Digital Inquiry Group</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2b4d669597746dfbbb7bc92fff12f5d-director-of-operations-partnerships-coo-equivalent-digital-inquiry-group-palo-alto</t>
+  </si>
+  <si>
     <t>Director of Policy &amp; Coalition Building</t>
   </si>
   <si>
@@ -946,12 +1258,24 @@
     <t>USD 135000.00 - 165000.00/year</t>
   </si>
   <si>
-    <t>Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/fa5a082e26b2407e8b866e4ba3cb8c54-director-of-policy-coalition-building-public-counsel-los-angeles</t>
   </si>
   <si>
+    <t>Director, Corporate &amp; Strategic Partnerships</t>
+  </si>
+  <si>
+    <t>Shatterproof</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41b2e785c4f94c0d84b10d4e4ef096bc-director-corporate-strategic-partnerships-shatterproof-norwalk</t>
+  </si>
+  <si>
     <t>Director, Tax Policy</t>
   </si>
   <si>
@@ -979,6 +1303,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c8068dd2c4ac4cd3abdec02f74750547-disability-employment-specialist-job-path-inc-new-york</t>
   </si>
   <si>
+    <t>Disaster Relief Coordinator</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c05581539281421a992d9019e531310e-disaster-relief-coordinator-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Domestic Violence Counselor-Coordinated Safety Response Program</t>
   </si>
   <si>
@@ -1021,9 +1360,6 @@
     <t>Framingham, Massachusetts</t>
   </si>
   <si>
-    <t>USD 75000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Education, Arts Music, Civic Engagement</t>
   </si>
   <si>
@@ -1045,6 +1381,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/65f89908f10447fbb38747ae21c5a0eb-executive-director-lopez-community-land-trust-lopez-island</t>
   </si>
   <si>
+    <t>Aurora Commons</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/555bf64356f346fe879ae7804c149458-executive-director-aurora-commons-seattle</t>
+  </si>
+  <si>
+    <t>Executive Director, Norris</t>
+  </si>
+  <si>
+    <t>Norris, Inc.</t>
+  </si>
+  <si>
+    <t>Mukwonago, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4f0ebd41e9cc4049bda5b965a669cc82-executive-director-norris-norris-inc-mukwonago</t>
+  </si>
+  <si>
+    <t>Exit Case Manager</t>
+  </si>
+  <si>
+    <t>Life After Hate, Inc</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a4accb9e652d480c97026111ac913ea5-exit-case-manager-life-after-hate-inc-milwaukee</t>
+  </si>
+  <si>
     <t>Financial Reporting Manager</t>
   </si>
   <si>
@@ -1063,6 +1447,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/cc98734a85624c51af35ccdf3fd4bba6-financial-reporting-manager-american-speech-language-hearing-association-rockville</t>
   </si>
   <si>
+    <t>Full Charge Bookkeeper</t>
+  </si>
+  <si>
+    <t>USD 31.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b0cb3b0ac7742018ac076d8eb68af89-full-charge-bookkeeper-seva-foundation-berkeley</t>
+  </si>
+  <si>
+    <t>Full-Time Field Lead Position at Three Springs Community Farm</t>
+  </si>
+  <si>
+    <t>Three Springs Community Farm Foundation</t>
+  </si>
+  <si>
+    <t>Freestone, CA</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c90936048e6454facbf1a18b42a3b41-full-time-field-lead-position-at-three-springs-community-farm-three-springs-community-farm-foundation-freestone</t>
+  </si>
+  <si>
     <t>Full-Time Operations Manager</t>
   </si>
   <si>
@@ -1081,9 +1492,6 @@
     <t>ARTISTIC VOICES INC</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 400.00 - 400.00/month</t>
   </si>
   <si>
@@ -1093,6 +1501,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/38409a4141b14bccbc45d986f819e5d0-fundraising-manager-artistic-voices-inc-miami</t>
   </si>
   <si>
+    <t>Gift Entry Holiday Fundraising Position</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6c7092b932a43a78f2fdd34b6b7180f-gift-entry-holiday-fundraising-position-seva-foundation-berkeley</t>
+  </si>
+  <si>
     <t>Graphic &amp; Multimedia Coordinator</t>
   </si>
   <si>
@@ -1123,6 +1543,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/c3f2f8ce6359480db8e48cc2cf7f44fa-home-tutors-hyderabad-telangana-shivas-tutorial-hyderabad</t>
   </si>
   <si>
+    <t>Human Resources Business Partner</t>
+  </si>
+  <si>
+    <t>Neighborhood Health</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54defde1f5ee4028a6b2e4863a43be50-human-resources-business-partner-neighborhood-health-alexandria</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Brink Literacy Project</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Mental Health, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2ff65a48bcfa40c4804bd8d57eccfc16-instructor-brink-literacy-project-denver</t>
+  </si>
+  <si>
     <t>Interim/Permanent Traditional Worship Accompanist (Organ &amp; Piano)</t>
   </si>
   <si>
@@ -1171,6 +1621,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/eaeade1ec6494244b1df97c9b8fc9a7b-learning-and-impact-manager-multiplier-san-francisco</t>
   </si>
   <si>
+    <t>Legal Content Manager, Content Intern and Fellow Program</t>
+  </si>
+  <si>
+    <t>Illinois Legal Aid Online (ILAO)</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f121c9b4e6ac464d889123e3a6e0d1ae-legal-content-manager-content-intern-and-fellow-program-illinois-legal-aid-online-ilao-chicago</t>
+  </si>
+  <si>
+    <t>Legal Content Manager, Volunteer Programs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad42f47d2e714c48bc56d461448f4d2d-legal-content-manager-volunteer-programs-illinois-legal-aid-online-ilao-chicago</t>
+  </si>
+  <si>
+    <t>Legislative Advocacy Fellow</t>
+  </si>
+  <si>
+    <t>Our Children Oregon</t>
+  </si>
+  <si>
+    <t>Remote (Oregon)</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce840fe996cf4bef809d43272df00c8a-legislative-advocacy-fellow-our-children-oregon-portland</t>
+  </si>
+  <si>
     <t>Manager of Grants and Project Support</t>
   </si>
   <si>
@@ -1216,9 +1708,6 @@
     <t>USD 52000.00 - 55000.00/year</t>
   </si>
   <si>
-    <t>Children Youth</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/847bf3d47b294540a16276be63e89107-membership-retention-specialist-girl-scout-council-of-the-nations-capital-martinsburg</t>
   </si>
   <si>
@@ -1240,6 +1729,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a475c63497104ccca45f71b531f9c7c6-mental-health-rehabilitation-counselor-full-time-southern-tier-environments-for-living-inc-gowanda</t>
   </si>
   <si>
+    <t>Mural Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Groundswell Community Mural Project</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a84cff981d648fcbd66f9916c9d82a0-mural-operations-coordinator-groundswell-community-mural-project-brooklyn</t>
+  </si>
+  <si>
     <t>Nonprofit Mobilization Coordinator</t>
   </si>
   <si>
@@ -1309,15 +1816,42 @@
     <t>Half Moon Bay, California</t>
   </si>
   <si>
-    <t>USD 90000.00 - 110000.00/year</t>
-  </si>
-  <si>
     <t>Community Development, Economic Development, Entrepreneurship</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/580470ac2fa94707b4acc4b28c720b0a-peninsula-program-manager-coastside-renaissance-entrepreneurship-center-half-moon-bay</t>
   </si>
   <si>
+    <t>Policy Director</t>
+  </si>
+  <si>
+    <t>MOVE Texas</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90041.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc7f146ceead498bb655a6b41c0429cf-policy-director-move-texas-austin</t>
+  </si>
+  <si>
+    <t>President &amp; CEO</t>
+  </si>
+  <si>
+    <t>Chesapeake Region Accessible Boating</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/20375032c29d41ac88e67663e4a63acf-president-ceo-chesapeake-region-accessible-boating-annapolis</t>
+  </si>
+  <si>
     <t>Program Manager</t>
   </si>
   <si>
@@ -1345,6 +1879,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/598667dece8a446ba4788598f96dc28d-programs-coordinator-full-time-remote-marys-meals-usa-bloomfield</t>
   </si>
   <si>
+    <t>Research Analyst - New Organizing SEIU Healthcare Michigan (HCMI)</t>
+  </si>
+  <si>
+    <t>SEIU</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c3e358cc197c4c11b821cddb0635c558-research-analyst-new-organizing-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
+  </si>
+  <si>
     <t>Research and Strategic Initiatives Manager</t>
   </si>
   <si>
@@ -1402,6 +1954,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/98eed4fc5d424eecaa5c45afcb5c1666-senior-accountant-institute-for-energy-economics-and-financial-analysis-lakewood</t>
   </si>
   <si>
+    <t>Senior Advisor to the President</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bb2debd654b4c1b96c1f97da5bf22e1-senior-advisor-to-the-president-fb-heron-foundation-birmingham</t>
+  </si>
+  <si>
     <t>Senior Advisor, Vaccine &amp; Clinical Case Management</t>
   </si>
   <si>
@@ -1444,15 +2005,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/17cbafb3bd8a44b084ef912b40671fc5-senior-associate-portfolio-management-rsf-social-finance-san-francisco</t>
   </si>
   <si>
+    <t>Senior Data &amp; Systems Analyst</t>
+  </si>
+  <si>
+    <t>SPEND Initiative</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4dd46c467ba428d949374a6fe1e8df5-senior-data-systems-analyst-spend-initiative-watertown</t>
+  </si>
+  <si>
     <t>Senior Director - Management and Administration</t>
   </si>
   <si>
     <t>Center Theatre Group via TOC Arts Partners</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 180000.00 - 200000.00/year</t>
   </si>
   <si>
@@ -1462,6 +2032,24 @@
     <t>https://www.idealist.org/en/job/c2ab4dc9053342c2bf5efed6c2161d37-senior-director-management-and-administration-center-theatre-group-via-toc-arts-partners-los-angeles</t>
   </si>
   <si>
+    <t>SENIOR HUMAN RESOURCES MANAGER</t>
+  </si>
+  <si>
+    <t>Partners for Justice</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a62fbbde54a2487da9a1ee332347b1ea-senior-human-resources-manager-partners-for-justice-los-angeles</t>
+  </si>
+  <si>
     <t>Senior Major Gifts Officer</t>
   </si>
   <si>
@@ -1471,6 +2059,21 @@
     <t>https://www.idealist.org/en/job/0e103068f03c47a5b2226dfd363fecbc-senior-major-gifts-officer-american-museum-of-natural-history-new-york</t>
   </si>
   <si>
+    <t>Senior Project Manager, Business Applications &amp; Solutions</t>
+  </si>
+  <si>
+    <t>Open Space Institute</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fb2b95aed624fe88375c3cf17f50ca4-senior-project-manager-business-applications-solutions-open-space-institute-new-york</t>
+  </si>
+  <si>
     <t>Site Manager</t>
   </si>
   <si>
@@ -1489,6 +2092,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/02ef85ba262142ad9b99b60faf1ec75c-site-manager-gigis-playhouse-hillsborough-hillsborough-township</t>
   </si>
   <si>
+    <t>Special Assistant</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/dd711b2fd2b04e3dad3bc757f518ec28-special-assistant-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>MALDEF - Mexican American Legal Defense and Educational Fund</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/734e510ce2a742f7a573a9a1356459b1-staff-accountant-maldef-mexican-american-legal-defense-and-educational-fund-los-angeles</t>
+  </si>
+  <si>
     <t>Staff Associate I</t>
   </si>
   <si>
@@ -1552,6 +2185,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/6db6346534d348d581c8d27fb7143df4-temporary-paralegal-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
+    <t>Trabajadora de Salud Comunitaria-Salvador Urbina</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Salvador Urbina, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 6500.00 - 6500.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d88530a61d9644ad95a785735391451c-trabajadora-de-salud-comunitaria-salvador-urbina-companeros-en-salud-salvador-urbina</t>
+  </si>
+  <si>
     <t>Trauma Therapist - Full-Time - Counseling Center</t>
   </si>
   <si>
@@ -1570,9 +2221,6 @@
     <t>USD 50000.00 - 52000.00/year</t>
   </si>
   <si>
-    <t>Animals</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/64c6e2925bde4311be033ec456d6ecdc-undercover-investigator-animal-equality-los-angeles</t>
   </si>
   <si>
@@ -1585,6 +2233,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/4963ba2267ad48db918e2c5e19896e7c-undercover-investigator-germany-animal-equality-los-angeles</t>
   </si>
   <si>
+    <t>Vice President for Finance</t>
+  </si>
+  <si>
+    <t>Society for the Protection of NH Forests</t>
+  </si>
+  <si>
+    <t>Concord, NH</t>
+  </si>
+  <si>
+    <t>USD 105000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d7832fed56c4b2eb30ed92e6977a4f9-vice-president-for-finance-society-for-the-protection-of-nh-forests-concord</t>
+  </si>
+  <si>
+    <t>Washington New American's Lead Attorney</t>
+  </si>
+  <si>
+    <t>OneAmerica</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6de9cc1eb39439d8e1dcffc102fe420-washington-new-americans-lead-attorney-oneamerica-seattle</t>
+  </si>
+  <si>
     <t>Writing Instructor</t>
   </si>
   <si>
@@ -1594,27 +2275,27 @@
     <t>Long Is City, New York</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
-    <t>USD 25.00 - 25.00/hour</t>
-  </si>
-  <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3895ee8a359e45f29a2655408e8c0453-writing-instructor-legal-outreach-long-is-city</t>
   </si>
   <si>
+    <t>Youth Advocate</t>
+  </si>
+  <si>
+    <t>HopeWell Inc.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d00bc17a1394548bd85ef88cacba4a0-youth-advocate-hopewell-inc-boston</t>
+  </si>
+  <si>
     <t>AGENCY RELATIONS COORDINATOR</t>
   </si>
   <si>
     <t>Food Lifeline</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>Program Operations</t>
   </si>
   <si>
@@ -1828,9 +2509,6 @@
     <t>Ecology Center</t>
   </si>
   <si>
-    <t>Berkeley, California</t>
-  </si>
-  <si>
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73946565</t>
   </si>
   <si>
@@ -1957,9 +2635,6 @@
     <t>Make Food Not Waste</t>
   </si>
   <si>
-    <t>Detroit, Michigan</t>
-  </si>
-  <si>
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73953897</t>
   </si>
   <si>
@@ -2009,9 +2684,6 @@
   </si>
   <si>
     <t>City of Denver</t>
-  </si>
-  <si>
-    <t>Denver, Colorado</t>
   </si>
   <si>
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73991779</t>
@@ -3115,7 +3787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3188,536 +3860,536 @@
         <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F4" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="F5" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="F9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="F12" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C14" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F15" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B16" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C16" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="D17" t="s">
         <v>152</v>
       </c>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F17" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B19" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C19" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F19" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B20" t="s">
         <v>245</v>
       </c>
-      <c r="B20" t="s">
-        <v>246</v>
-      </c>
       <c r="C20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" t="s">
         <v>247</v>
       </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" t="s">
-        <v>248</v>
-      </c>
       <c r="F20" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C21" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C23" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>265</v>
       </c>
       <c r="F23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
       </c>
       <c r="E24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
         <v>276</v>
       </c>
       <c r="F25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" t="s">
         <v>279</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>280</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>281</v>
-      </c>
-      <c r="D26" t="s">
-        <v>152</v>
       </c>
       <c r="E26" t="s">
         <v>282</v>
@@ -3740,36 +4412,36 @@
         <v>287</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>288</v>
       </c>
       <c r="F27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F28" t="s">
-        <v>293</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>294</v>
@@ -3786,904 +4458,904 @@
         <v>297</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
         <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C31" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F31" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>315</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F32" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C33" t="s">
-        <v>185</v>
+        <v>321</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="E33" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F33" t="s">
-        <v>146</v>
+        <v>323</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F34" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C35" t="s">
-        <v>329</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F35" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C36" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F36" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C37" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E37" t="s">
-        <v>340</v>
+        <v>146</v>
       </c>
       <c r="F37" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C38" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D38" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F38" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C39" t="s">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F39" t="s">
-        <v>260</v>
+        <v>354</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C40" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="D40" t="s">
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="E40" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F40" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C41" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>146</v>
+        <v>365</v>
       </c>
       <c r="F41" t="s">
-        <v>146</v>
+        <v>366</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C42" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
-        <v>366</v>
+        <v>146</v>
       </c>
       <c r="F42" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C43" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D43" t="s">
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F43" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C44" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D44" t="s">
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="F44" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s">
-        <v>263</v>
+        <v>386</v>
       </c>
       <c r="C45" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F45" t="s">
-        <v>265</v>
+        <v>388</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C46" t="s">
-        <v>247</v>
+        <v>392</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F46" t="s">
-        <v>383</v>
+        <v>200</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C47" t="s">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E47" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F47" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C48" t="s">
-        <v>219</v>
+        <v>401</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E48" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F48" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C49" t="s">
-        <v>398</v>
+        <v>327</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F49" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C50" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E50" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="F50" t="s">
-        <v>406</v>
+        <v>242</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E51" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="F51" t="s">
-        <v>146</v>
+        <v>418</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C52" t="s">
-        <v>413</v>
+        <v>254</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E52" t="s">
-        <v>351</v>
+        <v>422</v>
       </c>
       <c r="F52" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D53" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E53" t="s">
-        <v>248</v>
+        <v>427</v>
       </c>
       <c r="F53" t="s">
-        <v>414</v>
+        <v>146</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C54" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E54" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F54" t="s">
-        <v>310</v>
+        <v>432</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s">
-        <v>350</v>
+        <v>435</v>
       </c>
       <c r="C55" t="s">
-        <v>185</v>
+        <v>436</v>
       </c>
       <c r="D55" t="s">
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="E55" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="F55" t="s">
-        <v>260</v>
+        <v>438</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>441</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>442</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E56" t="s">
-        <v>146</v>
+        <v>443</v>
       </c>
       <c r="F56" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>428</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="C57" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>431</v>
+        <v>187</v>
       </c>
       <c r="F57" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>434</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C58" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="D58" t="s">
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>146</v>
+        <v>452</v>
       </c>
       <c r="F58" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>439</v>
+        <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C59" t="s">
-        <v>247</v>
+        <v>456</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>146</v>
+        <v>457</v>
       </c>
       <c r="F59" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>462</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E60" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F60" t="s">
-        <v>146</v>
+        <v>464</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="C61" t="s">
-        <v>449</v>
+        <v>327</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="E61" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="F61" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B62" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C62" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E62" t="s">
-        <v>146</v>
+        <v>474</v>
       </c>
       <c r="F62" t="s">
-        <v>146</v>
+        <v>475</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s">
-        <v>458</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E63" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="F63" t="s">
-        <v>460</v>
+        <v>154</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="B64" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="C64" t="s">
-        <v>247</v>
+        <v>482</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="F64" t="s">
-        <v>265</v>
+        <v>484</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="C65" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="F65" t="s">
-        <v>469</v>
+        <v>340</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="B66" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="C66" t="s">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="D66" t="s">
         <v>152</v>
       </c>
       <c r="E66" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="F66" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B67" t="s">
-        <v>477</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>478</v>
+        <v>151</v>
       </c>
       <c r="D67" t="s">
-        <v>152</v>
+        <v>496</v>
       </c>
       <c r="E67" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="F67" t="s">
-        <v>480</v>
+        <v>154</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="C68" t="s">
-        <v>185</v>
+        <v>501</v>
       </c>
       <c r="D68" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E68" t="s">
         <v>146</v>
@@ -4692,283 +5364,1341 @@
         <v>146</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="C69" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D69" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="E69" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="F69" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="C70" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="F70" t="s">
         <v>146</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B71" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>515</v>
       </c>
       <c r="D71" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E71" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="F71" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s">
-        <v>419</v>
+        <v>520</v>
       </c>
       <c r="C72" t="s">
-        <v>185</v>
+        <v>521</v>
       </c>
       <c r="D72" t="s">
         <v>152</v>
       </c>
       <c r="E72" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="F72" t="s">
-        <v>310</v>
+        <v>523</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s">
-        <v>296</v>
+        <v>520</v>
       </c>
       <c r="C73" t="s">
-        <v>297</v>
+        <v>521</v>
       </c>
       <c r="D73" t="s">
         <v>152</v>
       </c>
       <c r="E73" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="F73" t="s">
-        <v>212</v>
+        <v>523</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s">
-        <v>419</v>
+        <v>343</v>
       </c>
       <c r="C74" t="s">
-        <v>185</v>
+        <v>344</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E74" t="s">
-        <v>146</v>
+        <v>528</v>
       </c>
       <c r="F74" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>506</v>
+        <v>529</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s">
-        <v>318</v>
+        <v>531</v>
       </c>
       <c r="C75" t="s">
-        <v>185</v>
+        <v>327</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E75" t="s">
-        <v>319</v>
+        <v>532</v>
       </c>
       <c r="F75" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="B76" t="s">
-        <v>419</v>
+        <v>536</v>
       </c>
       <c r="C76" t="s">
-        <v>185</v>
+        <v>537</v>
       </c>
       <c r="D76" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E76" t="s">
-        <v>420</v>
+        <v>538</v>
       </c>
       <c r="F76" t="s">
-        <v>310</v>
+        <v>539</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>511</v>
+        <v>540</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="B77" t="s">
-        <v>224</v>
+        <v>536</v>
       </c>
       <c r="C77" t="s">
-        <v>185</v>
+        <v>537</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="F77" t="s">
-        <v>226</v>
+        <v>539</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="B78" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="C78" t="s">
-        <v>247</v>
+        <v>545</v>
       </c>
       <c r="D78" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="E78" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="F78" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>519</v>
+        <v>548</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="B79" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="C79" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="D79" t="s">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="E79" t="s">
-        <v>146</v>
+        <v>552</v>
       </c>
       <c r="F79" t="s">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="B80" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="C80" t="s">
-        <v>525</v>
+        <v>254</v>
       </c>
       <c r="D80" t="s">
-        <v>526</v>
+        <v>159</v>
       </c>
       <c r="E80" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="F80" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>529</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>560</v>
+      </c>
+      <c r="B81" t="s">
+        <v>561</v>
+      </c>
+      <c r="C81" t="s">
+        <v>562</v>
+      </c>
+      <c r="D81" t="s">
+        <v>159</v>
+      </c>
+      <c r="E81" t="s">
+        <v>563</v>
+      </c>
+      <c r="F81" t="s">
+        <v>432</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>565</v>
+      </c>
+      <c r="B82" t="s">
+        <v>566</v>
+      </c>
+      <c r="C82" t="s">
+        <v>567</v>
+      </c>
+      <c r="D82" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" t="s">
+        <v>568</v>
+      </c>
+      <c r="F82" t="s">
+        <v>569</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>571</v>
+      </c>
+      <c r="B83" t="s">
+        <v>572</v>
+      </c>
+      <c r="C83" t="s">
+        <v>573</v>
+      </c>
+      <c r="D83" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" t="s">
+        <v>574</v>
+      </c>
+      <c r="F83" t="s">
+        <v>575</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>577</v>
+      </c>
+      <c r="B84" t="s">
+        <v>578</v>
+      </c>
+      <c r="C84" t="s">
+        <v>327</v>
+      </c>
+      <c r="D84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" t="s">
+        <v>552</v>
+      </c>
+      <c r="F84" t="s">
+        <v>146</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>580</v>
+      </c>
+      <c r="B85" t="s">
+        <v>581</v>
+      </c>
+      <c r="C85" t="s">
+        <v>582</v>
+      </c>
+      <c r="D85" t="s">
+        <v>159</v>
+      </c>
+      <c r="E85" t="s">
+        <v>488</v>
+      </c>
+      <c r="F85" t="s">
+        <v>583</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>585</v>
+      </c>
+      <c r="B86" t="s">
+        <v>581</v>
+      </c>
+      <c r="C86" t="s">
+        <v>254</v>
+      </c>
+      <c r="D86" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" t="s">
+        <v>328</v>
+      </c>
+      <c r="F86" t="s">
+        <v>583</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>587</v>
+      </c>
+      <c r="B87" t="s">
+        <v>588</v>
+      </c>
+      <c r="C87" t="s">
+        <v>204</v>
+      </c>
+      <c r="D87" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" t="s">
+        <v>589</v>
+      </c>
+      <c r="F87" t="s">
+        <v>242</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>591</v>
+      </c>
+      <c r="B88" t="s">
+        <v>487</v>
+      </c>
+      <c r="C88" t="s">
+        <v>204</v>
+      </c>
+      <c r="D88" t="s">
+        <v>152</v>
+      </c>
+      <c r="E88" t="s">
+        <v>592</v>
+      </c>
+      <c r="F88" t="s">
+        <v>340</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>594</v>
+      </c>
+      <c r="B89" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" t="s">
+        <v>192</v>
+      </c>
+      <c r="D89" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" t="s">
+        <v>146</v>
+      </c>
+      <c r="F89" t="s">
+        <v>595</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>597</v>
+      </c>
+      <c r="B90" t="s">
+        <v>598</v>
+      </c>
+      <c r="C90" t="s">
+        <v>599</v>
+      </c>
+      <c r="D90" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" t="s">
+        <v>353</v>
+      </c>
+      <c r="F90" t="s">
+        <v>600</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>602</v>
+      </c>
+      <c r="B91" t="s">
+        <v>603</v>
+      </c>
+      <c r="C91" t="s">
+        <v>297</v>
+      </c>
+      <c r="D91" t="s">
+        <v>159</v>
+      </c>
+      <c r="E91" t="s">
+        <v>604</v>
+      </c>
+      <c r="F91" t="s">
+        <v>605</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>607</v>
+      </c>
+      <c r="B92" t="s">
+        <v>608</v>
+      </c>
+      <c r="C92" t="s">
+        <v>609</v>
+      </c>
+      <c r="D92" t="s">
+        <v>159</v>
+      </c>
+      <c r="E92" t="s">
+        <v>610</v>
+      </c>
+      <c r="F92" t="s">
+        <v>575</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>612</v>
+      </c>
+      <c r="B93" t="s">
+        <v>613</v>
+      </c>
+      <c r="C93" t="s">
+        <v>614</v>
+      </c>
+      <c r="D93" t="s">
+        <v>152</v>
+      </c>
+      <c r="E93" t="s">
+        <v>146</v>
+      </c>
+      <c r="F93" t="s">
+        <v>615</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>617</v>
+      </c>
+      <c r="B94" t="s">
+        <v>618</v>
+      </c>
+      <c r="C94" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94" t="s">
+        <v>159</v>
+      </c>
+      <c r="E94" t="s">
+        <v>146</v>
+      </c>
+      <c r="F94" t="s">
+        <v>619</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>621</v>
+      </c>
+      <c r="B95" t="s">
+        <v>622</v>
+      </c>
+      <c r="C95" t="s">
+        <v>623</v>
+      </c>
+      <c r="D95" t="s">
+        <v>624</v>
+      </c>
+      <c r="E95" t="s">
+        <v>625</v>
+      </c>
+      <c r="F95" t="s">
+        <v>146</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>627</v>
+      </c>
+      <c r="B96" t="s">
+        <v>628</v>
+      </c>
+      <c r="C96" t="s">
+        <v>327</v>
+      </c>
+      <c r="D96" t="s">
+        <v>159</v>
+      </c>
+      <c r="E96" t="s">
+        <v>629</v>
+      </c>
+      <c r="F96" t="s">
+        <v>146</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>631</v>
+      </c>
+      <c r="B97" t="s">
+        <v>632</v>
+      </c>
+      <c r="C97" t="s">
+        <v>633</v>
+      </c>
+      <c r="D97" t="s">
+        <v>159</v>
+      </c>
+      <c r="E97" t="s">
+        <v>634</v>
+      </c>
+      <c r="F97" t="s">
+        <v>635</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>637</v>
+      </c>
+      <c r="B98" t="s">
+        <v>638</v>
+      </c>
+      <c r="C98" t="s">
+        <v>639</v>
+      </c>
+      <c r="D98" t="s">
+        <v>159</v>
+      </c>
+      <c r="E98" t="s">
+        <v>146</v>
+      </c>
+      <c r="F98" t="s">
+        <v>146</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>641</v>
+      </c>
+      <c r="B99" t="s">
+        <v>642</v>
+      </c>
+      <c r="C99" t="s">
+        <v>327</v>
+      </c>
+      <c r="D99" t="s">
+        <v>159</v>
+      </c>
+      <c r="E99" t="s">
+        <v>643</v>
+      </c>
+      <c r="F99" t="s">
+        <v>644</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>646</v>
+      </c>
+      <c r="B100" t="s">
+        <v>308</v>
+      </c>
+      <c r="C100" t="s">
+        <v>309</v>
+      </c>
+      <c r="D100" t="s">
+        <v>159</v>
+      </c>
+      <c r="E100" t="s">
+        <v>647</v>
+      </c>
+      <c r="F100" t="s">
+        <v>311</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>649</v>
+      </c>
+      <c r="B101" t="s">
+        <v>650</v>
+      </c>
+      <c r="C101" t="s">
+        <v>327</v>
+      </c>
+      <c r="D101" t="s">
+        <v>159</v>
+      </c>
+      <c r="E101" t="s">
+        <v>651</v>
+      </c>
+      <c r="F101" t="s">
+        <v>154</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>653</v>
+      </c>
+      <c r="B102" t="s">
+        <v>654</v>
+      </c>
+      <c r="C102" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" t="s">
+        <v>159</v>
+      </c>
+      <c r="E102" t="s">
+        <v>655</v>
+      </c>
+      <c r="F102" t="s">
+        <v>656</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>658</v>
+      </c>
+      <c r="B103" t="s">
+        <v>659</v>
+      </c>
+      <c r="C103" t="s">
+        <v>327</v>
+      </c>
+      <c r="D103" t="s">
+        <v>159</v>
+      </c>
+      <c r="E103" t="s">
+        <v>660</v>
+      </c>
+      <c r="F103" t="s">
+        <v>661</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>663</v>
+      </c>
+      <c r="B104" t="s">
+        <v>664</v>
+      </c>
+      <c r="C104" t="s">
+        <v>327</v>
+      </c>
+      <c r="D104" t="s">
+        <v>159</v>
+      </c>
+      <c r="E104" t="s">
+        <v>353</v>
+      </c>
+      <c r="F104" t="s">
+        <v>665</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>667</v>
+      </c>
+      <c r="B105" t="s">
+        <v>668</v>
+      </c>
+      <c r="C105" t="s">
+        <v>198</v>
+      </c>
+      <c r="D105" t="s">
+        <v>159</v>
+      </c>
+      <c r="E105" t="s">
+        <v>669</v>
+      </c>
+      <c r="F105" t="s">
+        <v>670</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>672</v>
+      </c>
+      <c r="B106" t="s">
+        <v>673</v>
+      </c>
+      <c r="C106" t="s">
+        <v>674</v>
+      </c>
+      <c r="D106" t="s">
+        <v>159</v>
+      </c>
+      <c r="E106" t="s">
+        <v>675</v>
+      </c>
+      <c r="F106" t="s">
+        <v>676</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>678</v>
+      </c>
+      <c r="B107" t="s">
+        <v>679</v>
+      </c>
+      <c r="C107" t="s">
+        <v>204</v>
+      </c>
+      <c r="D107" t="s">
+        <v>159</v>
+      </c>
+      <c r="E107" t="s">
+        <v>146</v>
+      </c>
+      <c r="F107" t="s">
+        <v>146</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>681</v>
+      </c>
+      <c r="B108" t="s">
+        <v>682</v>
+      </c>
+      <c r="C108" t="s">
+        <v>204</v>
+      </c>
+      <c r="D108" t="s">
+        <v>159</v>
+      </c>
+      <c r="E108" t="s">
+        <v>683</v>
+      </c>
+      <c r="F108" t="s">
+        <v>684</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>686</v>
+      </c>
+      <c r="B109" t="s">
+        <v>687</v>
+      </c>
+      <c r="C109" t="s">
+        <v>688</v>
+      </c>
+      <c r="D109" t="s">
+        <v>159</v>
+      </c>
+      <c r="E109" t="s">
+        <v>689</v>
+      </c>
+      <c r="F109" t="s">
+        <v>690</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>692</v>
+      </c>
+      <c r="B110" t="s">
+        <v>693</v>
+      </c>
+      <c r="C110" t="s">
+        <v>254</v>
+      </c>
+      <c r="D110" t="s">
+        <v>159</v>
+      </c>
+      <c r="E110" t="s">
+        <v>694</v>
+      </c>
+      <c r="F110" t="s">
+        <v>695</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>697</v>
+      </c>
+      <c r="B111" t="s">
+        <v>698</v>
+      </c>
+      <c r="C111" t="s">
+        <v>198</v>
+      </c>
+      <c r="D111" t="s">
+        <v>159</v>
+      </c>
+      <c r="E111" t="s">
+        <v>699</v>
+      </c>
+      <c r="F111" t="s">
+        <v>700</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>702</v>
+      </c>
+      <c r="B112" t="s">
+        <v>703</v>
+      </c>
+      <c r="C112" t="s">
+        <v>204</v>
+      </c>
+      <c r="D112" t="s">
+        <v>159</v>
+      </c>
+      <c r="E112" t="s">
+        <v>704</v>
+      </c>
+      <c r="F112" t="s">
+        <v>146</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>706</v>
+      </c>
+      <c r="B113" t="s">
+        <v>707</v>
+      </c>
+      <c r="C113" t="s">
+        <v>158</v>
+      </c>
+      <c r="D113" t="s">
+        <v>159</v>
+      </c>
+      <c r="E113" t="s">
+        <v>708</v>
+      </c>
+      <c r="F113" t="s">
+        <v>709</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>706</v>
+      </c>
+      <c r="B114" t="s">
+        <v>588</v>
+      </c>
+      <c r="C114" t="s">
+        <v>204</v>
+      </c>
+      <c r="D114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E114" t="s">
+        <v>711</v>
+      </c>
+      <c r="F114" t="s">
+        <v>242</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>713</v>
+      </c>
+      <c r="B115" t="s">
+        <v>391</v>
+      </c>
+      <c r="C115" t="s">
+        <v>392</v>
+      </c>
+      <c r="D115" t="s">
+        <v>159</v>
+      </c>
+      <c r="E115" t="s">
+        <v>714</v>
+      </c>
+      <c r="F115" t="s">
+        <v>200</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>716</v>
+      </c>
+      <c r="B116" t="s">
+        <v>588</v>
+      </c>
+      <c r="C116" t="s">
+        <v>204</v>
+      </c>
+      <c r="D116" t="s">
+        <v>159</v>
+      </c>
+      <c r="E116" t="s">
+        <v>146</v>
+      </c>
+      <c r="F116" t="s">
+        <v>242</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>718</v>
+      </c>
+      <c r="B117" t="s">
+        <v>426</v>
+      </c>
+      <c r="C117" t="s">
+        <v>204</v>
+      </c>
+      <c r="D117" t="s">
+        <v>159</v>
+      </c>
+      <c r="E117" t="s">
+        <v>427</v>
+      </c>
+      <c r="F117" t="s">
+        <v>719</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>721</v>
+      </c>
+      <c r="B118" t="s">
+        <v>588</v>
+      </c>
+      <c r="C118" t="s">
+        <v>204</v>
+      </c>
+      <c r="D118" t="s">
+        <v>159</v>
+      </c>
+      <c r="E118" t="s">
+        <v>589</v>
+      </c>
+      <c r="F118" t="s">
+        <v>242</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>723</v>
+      </c>
+      <c r="B119" t="s">
+        <v>724</v>
+      </c>
+      <c r="C119" t="s">
+        <v>725</v>
+      </c>
+      <c r="D119" t="s">
+        <v>496</v>
+      </c>
+      <c r="E119" t="s">
+        <v>726</v>
+      </c>
+      <c r="F119" t="s">
+        <v>727</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>729</v>
+      </c>
+      <c r="B120" t="s">
+        <v>264</v>
+      </c>
+      <c r="C120" t="s">
+        <v>204</v>
+      </c>
+      <c r="D120" t="s">
+        <v>159</v>
+      </c>
+      <c r="E120" t="s">
+        <v>730</v>
+      </c>
+      <c r="F120" t="s">
+        <v>266</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>732</v>
+      </c>
+      <c r="B121" t="s">
+        <v>733</v>
+      </c>
+      <c r="C121" t="s">
+        <v>327</v>
+      </c>
+      <c r="D121" t="s">
+        <v>159</v>
+      </c>
+      <c r="E121" t="s">
+        <v>734</v>
+      </c>
+      <c r="F121" t="s">
+        <v>377</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>736</v>
+      </c>
+      <c r="B122" t="s">
+        <v>733</v>
+      </c>
+      <c r="C122" t="s">
+        <v>737</v>
+      </c>
+      <c r="D122" t="s">
+        <v>281</v>
+      </c>
+      <c r="E122" t="s">
+        <v>146</v>
+      </c>
+      <c r="F122" t="s">
+        <v>377</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>739</v>
+      </c>
+      <c r="B123" t="s">
+        <v>740</v>
+      </c>
+      <c r="C123" t="s">
+        <v>741</v>
+      </c>
+      <c r="D123" t="s">
+        <v>159</v>
+      </c>
+      <c r="E123" t="s">
+        <v>742</v>
+      </c>
+      <c r="F123" t="s">
+        <v>743</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>745</v>
+      </c>
+      <c r="B124" t="s">
+        <v>746</v>
+      </c>
+      <c r="C124" t="s">
+        <v>456</v>
+      </c>
+      <c r="D124" t="s">
+        <v>159</v>
+      </c>
+      <c r="E124" t="s">
+        <v>747</v>
+      </c>
+      <c r="F124" t="s">
+        <v>748</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>750</v>
+      </c>
+      <c r="B125" t="s">
+        <v>751</v>
+      </c>
+      <c r="C125" t="s">
+        <v>752</v>
+      </c>
+      <c r="D125" t="s">
+        <v>496</v>
+      </c>
+      <c r="E125" t="s">
+        <v>235</v>
+      </c>
+      <c r="F125" t="s">
+        <v>230</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>754</v>
+      </c>
+      <c r="B126" t="s">
+        <v>755</v>
+      </c>
+      <c r="C126" t="s">
+        <v>158</v>
+      </c>
+      <c r="D126" t="s">
+        <v>159</v>
+      </c>
+      <c r="E126" t="s">
+        <v>756</v>
+      </c>
+      <c r="F126" t="s">
+        <v>547</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -5053,6 +6783,52 @@
     <hyperlink ref="H78" r:id="rId77"/>
     <hyperlink ref="H79" r:id="rId78"/>
     <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5102,13 +6878,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>530</v>
+        <v>758</v>
       </c>
       <c r="B2" t="s">
-        <v>531</v>
+        <v>759</v>
       </c>
       <c r="C2" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="D2" t="s">
         <v>146</v>
@@ -5117,21 +6893,21 @@
         <v>146</v>
       </c>
       <c r="F2" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>534</v>
+        <v>761</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>535</v>
+        <v>762</v>
       </c>
       <c r="B3" t="s">
-        <v>536</v>
+        <v>763</v>
       </c>
       <c r="C3" t="s">
-        <v>537</v>
+        <v>764</v>
       </c>
       <c r="D3" t="s">
         <v>146</v>
@@ -5140,21 +6916,21 @@
         <v>146</v>
       </c>
       <c r="F3" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>538</v>
+        <v>765</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>539</v>
+        <v>766</v>
       </c>
       <c r="B4" t="s">
-        <v>540</v>
+        <v>767</v>
       </c>
       <c r="C4" t="s">
-        <v>541</v>
+        <v>768</v>
       </c>
       <c r="D4" t="s">
         <v>146</v>
@@ -5163,21 +6939,21 @@
         <v>146</v>
       </c>
       <c r="F4" t="s">
-        <v>542</v>
+        <v>769</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>543</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>544</v>
+        <v>771</v>
       </c>
       <c r="B5" t="s">
-        <v>545</v>
+        <v>772</v>
       </c>
       <c r="C5" t="s">
-        <v>546</v>
+        <v>773</v>
       </c>
       <c r="D5" t="s">
         <v>146</v>
@@ -5186,21 +6962,21 @@
         <v>146</v>
       </c>
       <c r="F5" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>547</v>
+        <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>548</v>
+        <v>775</v>
       </c>
       <c r="B6" t="s">
-        <v>549</v>
+        <v>776</v>
       </c>
       <c r="C6" t="s">
-        <v>550</v>
+        <v>777</v>
       </c>
       <c r="D6" t="s">
         <v>146</v>
@@ -5209,21 +6985,21 @@
         <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>551</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>552</v>
+        <v>779</v>
       </c>
       <c r="B7" t="s">
-        <v>553</v>
+        <v>780</v>
       </c>
       <c r="C7" t="s">
-        <v>554</v>
+        <v>781</v>
       </c>
       <c r="D7" t="s">
         <v>146</v>
@@ -5232,21 +7008,21 @@
         <v>146</v>
       </c>
       <c r="F7" t="s">
-        <v>555</v>
+        <v>782</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>556</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>557</v>
+        <v>784</v>
       </c>
       <c r="B8" t="s">
-        <v>558</v>
+        <v>785</v>
       </c>
       <c r="C8" t="s">
-        <v>559</v>
+        <v>786</v>
       </c>
       <c r="D8" t="s">
         <v>146</v>
@@ -5255,21 +7031,21 @@
         <v>146</v>
       </c>
       <c r="F8" t="s">
-        <v>560</v>
+        <v>787</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>561</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>562</v>
+        <v>789</v>
       </c>
       <c r="B9" t="s">
-        <v>563</v>
+        <v>790</v>
       </c>
       <c r="C9" t="s">
-        <v>564</v>
+        <v>791</v>
       </c>
       <c r="D9" t="s">
         <v>146</v>
@@ -5278,21 +7054,21 @@
         <v>146</v>
       </c>
       <c r="F9" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>565</v>
+        <v>792</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>566</v>
+        <v>793</v>
       </c>
       <c r="B10" t="s">
-        <v>567</v>
+        <v>794</v>
       </c>
       <c r="C10" t="s">
-        <v>568</v>
+        <v>795</v>
       </c>
       <c r="D10" t="s">
         <v>146</v>
@@ -5301,21 +7077,21 @@
         <v>146</v>
       </c>
       <c r="F10" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>569</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>570</v>
+        <v>797</v>
       </c>
       <c r="B11" t="s">
-        <v>571</v>
+        <v>798</v>
       </c>
       <c r="C11" t="s">
-        <v>572</v>
+        <v>799</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
@@ -5324,21 +7100,21 @@
         <v>146</v>
       </c>
       <c r="F11" t="s">
-        <v>560</v>
+        <v>787</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>573</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>574</v>
+        <v>801</v>
       </c>
       <c r="B12" t="s">
-        <v>567</v>
+        <v>794</v>
       </c>
       <c r="C12" t="s">
-        <v>568</v>
+        <v>795</v>
       </c>
       <c r="D12" t="s">
         <v>146</v>
@@ -5347,21 +7123,21 @@
         <v>146</v>
       </c>
       <c r="F12" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>575</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>576</v>
+        <v>803</v>
       </c>
       <c r="B13" t="s">
-        <v>577</v>
+        <v>804</v>
       </c>
       <c r="C13" t="s">
-        <v>578</v>
+        <v>805</v>
       </c>
       <c r="D13" t="s">
         <v>146</v>
@@ -5370,21 +7146,21 @@
         <v>146</v>
       </c>
       <c r="F13" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>579</v>
+        <v>806</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>576</v>
+        <v>803</v>
       </c>
       <c r="B14" t="s">
-        <v>577</v>
+        <v>804</v>
       </c>
       <c r="C14" t="s">
-        <v>578</v>
+        <v>805</v>
       </c>
       <c r="D14" t="s">
         <v>146</v>
@@ -5393,21 +7169,21 @@
         <v>146</v>
       </c>
       <c r="F14" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>580</v>
+        <v>807</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>581</v>
+        <v>808</v>
       </c>
       <c r="B15" t="s">
-        <v>545</v>
+        <v>772</v>
       </c>
       <c r="C15" t="s">
-        <v>546</v>
+        <v>773</v>
       </c>
       <c r="D15" t="s">
         <v>146</v>
@@ -5416,21 +7192,21 @@
         <v>146</v>
       </c>
       <c r="F15" t="s">
-        <v>582</v>
+        <v>809</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>583</v>
+        <v>810</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>584</v>
+        <v>811</v>
       </c>
       <c r="B16" t="s">
-        <v>585</v>
+        <v>812</v>
       </c>
       <c r="C16" t="s">
-        <v>554</v>
+        <v>781</v>
       </c>
       <c r="D16" t="s">
         <v>146</v>
@@ -5439,21 +7215,21 @@
         <v>146</v>
       </c>
       <c r="F16" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>587</v>
+        <v>814</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>588</v>
+        <v>815</v>
       </c>
       <c r="B17" t="s">
-        <v>589</v>
+        <v>816</v>
       </c>
       <c r="C17" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="D17" t="s">
         <v>146</v>
@@ -5465,18 +7241,18 @@
         <v>56</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>590</v>
+        <v>817</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>591</v>
+        <v>818</v>
       </c>
       <c r="B18" t="s">
-        <v>592</v>
+        <v>819</v>
       </c>
       <c r="C18" t="s">
-        <v>554</v>
+        <v>781</v>
       </c>
       <c r="D18" t="s">
         <v>146</v>
@@ -5485,21 +7261,21 @@
         <v>146</v>
       </c>
       <c r="F18" t="s">
-        <v>542</v>
+        <v>769</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>593</v>
+        <v>820</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>594</v>
+        <v>821</v>
       </c>
       <c r="B19" t="s">
-        <v>595</v>
+        <v>822</v>
       </c>
       <c r="C19" t="s">
-        <v>596</v>
+        <v>823</v>
       </c>
       <c r="D19" t="s">
         <v>146</v>
@@ -5508,21 +7284,21 @@
         <v>146</v>
       </c>
       <c r="F19" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>597</v>
+        <v>824</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>598</v>
+        <v>825</v>
       </c>
       <c r="B20" t="s">
-        <v>599</v>
+        <v>826</v>
       </c>
       <c r="C20" t="s">
-        <v>600</v>
+        <v>827</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -5531,21 +7307,21 @@
         <v>146</v>
       </c>
       <c r="F20" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>601</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>602</v>
+        <v>829</v>
       </c>
       <c r="B21" t="s">
-        <v>603</v>
+        <v>830</v>
       </c>
       <c r="C21" t="s">
-        <v>604</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s">
         <v>146</v>
@@ -5554,21 +7330,21 @@
         <v>146</v>
       </c>
       <c r="F21" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>605</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>606</v>
+        <v>832</v>
       </c>
       <c r="B22" t="s">
-        <v>607</v>
+        <v>833</v>
       </c>
       <c r="C22" t="s">
-        <v>608</v>
+        <v>834</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -5577,21 +7353,21 @@
         <v>146</v>
       </c>
       <c r="F22" t="s">
-        <v>582</v>
+        <v>809</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>609</v>
+        <v>835</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>610</v>
+        <v>836</v>
       </c>
       <c r="B23" t="s">
-        <v>611</v>
+        <v>837</v>
       </c>
       <c r="C23" t="s">
-        <v>612</v>
+        <v>838</v>
       </c>
       <c r="D23" t="s">
         <v>146</v>
@@ -5600,21 +7376,21 @@
         <v>146</v>
       </c>
       <c r="F23" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>613</v>
+        <v>839</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>614</v>
+        <v>840</v>
       </c>
       <c r="B24" t="s">
-        <v>571</v>
+        <v>798</v>
       </c>
       <c r="C24" t="s">
-        <v>572</v>
+        <v>799</v>
       </c>
       <c r="D24" t="s">
         <v>146</v>
@@ -5623,21 +7399,21 @@
         <v>146</v>
       </c>
       <c r="F24" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>615</v>
+        <v>841</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>616</v>
+        <v>842</v>
       </c>
       <c r="B25" t="s">
-        <v>617</v>
+        <v>843</v>
       </c>
       <c r="C25" t="s">
-        <v>618</v>
+        <v>844</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -5646,21 +7422,21 @@
         <v>146</v>
       </c>
       <c r="F25" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>619</v>
+        <v>845</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>620</v>
+        <v>846</v>
       </c>
       <c r="B26" t="s">
-        <v>621</v>
+        <v>847</v>
       </c>
       <c r="C26" t="s">
-        <v>622</v>
+        <v>848</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -5669,21 +7445,21 @@
         <v>146</v>
       </c>
       <c r="F26" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>623</v>
+        <v>849</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>624</v>
+        <v>850</v>
       </c>
       <c r="B27" t="s">
-        <v>567</v>
+        <v>794</v>
       </c>
       <c r="C27" t="s">
-        <v>568</v>
+        <v>795</v>
       </c>
       <c r="D27" t="s">
         <v>146</v>
@@ -5692,21 +7468,21 @@
         <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>625</v>
+        <v>851</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>626</v>
+        <v>852</v>
       </c>
       <c r="B28" t="s">
-        <v>563</v>
+        <v>790</v>
       </c>
       <c r="C28" t="s">
-        <v>564</v>
+        <v>791</v>
       </c>
       <c r="D28" t="s">
         <v>146</v>
@@ -5715,21 +7491,21 @@
         <v>146</v>
       </c>
       <c r="F28" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>627</v>
+        <v>853</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>628</v>
+        <v>854</v>
       </c>
       <c r="B29" t="s">
-        <v>629</v>
+        <v>855</v>
       </c>
       <c r="C29" t="s">
-        <v>630</v>
+        <v>856</v>
       </c>
       <c r="D29" t="s">
         <v>146</v>
@@ -5738,21 +7514,21 @@
         <v>146</v>
       </c>
       <c r="F29" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>631</v>
+        <v>857</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>632</v>
+        <v>858</v>
       </c>
       <c r="B30" t="s">
-        <v>563</v>
+        <v>790</v>
       </c>
       <c r="C30" t="s">
-        <v>564</v>
+        <v>791</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -5761,21 +7537,21 @@
         <v>146</v>
       </c>
       <c r="F30" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>633</v>
+        <v>859</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>634</v>
+        <v>860</v>
       </c>
       <c r="B31" t="s">
-        <v>545</v>
+        <v>772</v>
       </c>
       <c r="C31" t="s">
-        <v>546</v>
+        <v>773</v>
       </c>
       <c r="D31" t="s">
         <v>146</v>
@@ -5784,21 +7560,21 @@
         <v>146</v>
       </c>
       <c r="F31" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>635</v>
+        <v>861</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>634</v>
+        <v>860</v>
       </c>
       <c r="B32" t="s">
-        <v>545</v>
+        <v>772</v>
       </c>
       <c r="C32" t="s">
-        <v>546</v>
+        <v>773</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -5807,21 +7583,21 @@
         <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>636</v>
+        <v>862</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>637</v>
+        <v>863</v>
       </c>
       <c r="B33" t="s">
-        <v>638</v>
+        <v>864</v>
       </c>
       <c r="C33" t="s">
-        <v>639</v>
+        <v>865</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -5830,21 +7606,21 @@
         <v>146</v>
       </c>
       <c r="F33" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>640</v>
+        <v>866</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>641</v>
+        <v>867</v>
       </c>
       <c r="B34" t="s">
-        <v>642</v>
+        <v>868</v>
       </c>
       <c r="C34" t="s">
-        <v>643</v>
+        <v>869</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -5853,21 +7629,21 @@
         <v>146</v>
       </c>
       <c r="F34" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>644</v>
+        <v>870</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>645</v>
+        <v>871</v>
       </c>
       <c r="B35" t="s">
-        <v>646</v>
+        <v>872</v>
       </c>
       <c r="C35" t="s">
-        <v>647</v>
+        <v>623</v>
       </c>
       <c r="D35" t="s">
         <v>146</v>
@@ -5876,21 +7652,21 @@
         <v>146</v>
       </c>
       <c r="F35" t="s">
-        <v>582</v>
+        <v>809</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>648</v>
+        <v>873</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>649</v>
+        <v>874</v>
       </c>
       <c r="B36" t="s">
-        <v>650</v>
+        <v>875</v>
       </c>
       <c r="C36" t="s">
-        <v>651</v>
+        <v>876</v>
       </c>
       <c r="D36" t="s">
         <v>146</v>
@@ -5899,21 +7675,21 @@
         <v>146</v>
       </c>
       <c r="F36" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>652</v>
+        <v>877</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>653</v>
+        <v>878</v>
       </c>
       <c r="B37" t="s">
-        <v>654</v>
+        <v>879</v>
       </c>
       <c r="C37" t="s">
-        <v>655</v>
+        <v>880</v>
       </c>
       <c r="D37" t="s">
         <v>146</v>
@@ -5922,21 +7698,21 @@
         <v>146</v>
       </c>
       <c r="F37" t="s">
-        <v>560</v>
+        <v>787</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>656</v>
+        <v>881</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>657</v>
+        <v>882</v>
       </c>
       <c r="B38" t="s">
-        <v>638</v>
+        <v>864</v>
       </c>
       <c r="C38" t="s">
-        <v>639</v>
+        <v>865</v>
       </c>
       <c r="D38" t="s">
         <v>146</v>
@@ -5945,21 +7721,21 @@
         <v>146</v>
       </c>
       <c r="F38" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>658</v>
+        <v>883</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>659</v>
+        <v>884</v>
       </c>
       <c r="B39" t="s">
-        <v>660</v>
+        <v>885</v>
       </c>
       <c r="C39" t="s">
-        <v>661</v>
+        <v>886</v>
       </c>
       <c r="D39" t="s">
         <v>146</v>
@@ -5968,21 +7744,21 @@
         <v>146</v>
       </c>
       <c r="F39" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>662</v>
+        <v>887</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>663</v>
+        <v>888</v>
       </c>
       <c r="B40" t="s">
-        <v>664</v>
+        <v>889</v>
       </c>
       <c r="C40" t="s">
-        <v>665</v>
+        <v>515</v>
       </c>
       <c r="D40" t="s">
         <v>146</v>
@@ -5991,21 +7767,21 @@
         <v>146</v>
       </c>
       <c r="F40" t="s">
-        <v>560</v>
+        <v>787</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>666</v>
+        <v>890</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>667</v>
+        <v>891</v>
       </c>
       <c r="B41" t="s">
-        <v>668</v>
+        <v>892</v>
       </c>
       <c r="C41" t="s">
-        <v>572</v>
+        <v>799</v>
       </c>
       <c r="D41" t="s">
         <v>146</v>
@@ -6014,21 +7790,21 @@
         <v>146</v>
       </c>
       <c r="F41" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>669</v>
+        <v>893</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>670</v>
+        <v>894</v>
       </c>
       <c r="B42" t="s">
-        <v>654</v>
+        <v>879</v>
       </c>
       <c r="C42" t="s">
-        <v>655</v>
+        <v>880</v>
       </c>
       <c r="D42" t="s">
         <v>146</v>
@@ -6037,21 +7813,21 @@
         <v>146</v>
       </c>
       <c r="F42" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>671</v>
+        <v>895</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>672</v>
+        <v>896</v>
       </c>
       <c r="B43" t="s">
-        <v>660</v>
+        <v>885</v>
       </c>
       <c r="C43" t="s">
-        <v>673</v>
+        <v>897</v>
       </c>
       <c r="D43" t="s">
         <v>146</v>
@@ -6060,21 +7836,21 @@
         <v>146</v>
       </c>
       <c r="F43" t="s">
-        <v>586</v>
+        <v>813</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>674</v>
+        <v>898</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>675</v>
+        <v>899</v>
       </c>
       <c r="B44" t="s">
-        <v>638</v>
+        <v>864</v>
       </c>
       <c r="C44" t="s">
-        <v>639</v>
+        <v>865</v>
       </c>
       <c r="D44" t="s">
         <v>146</v>
@@ -6083,21 +7859,21 @@
         <v>146</v>
       </c>
       <c r="F44" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>676</v>
+        <v>900</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>677</v>
+        <v>901</v>
       </c>
       <c r="B45" t="s">
-        <v>678</v>
+        <v>902</v>
       </c>
       <c r="C45" t="s">
-        <v>673</v>
+        <v>897</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -6106,10 +7882,10 @@
         <v>146</v>
       </c>
       <c r="F45" t="s">
-        <v>533</v>
+        <v>760</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>679</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
